--- a/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
+++ b/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
@@ -401,88 +401,88 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>psr_id</v>
+      </c>
+      <c r="B1" t="str">
+        <v>tahun_anggaran</v>
+      </c>
+      <c r="C1" t="str">
+        <v>nilai_kontrak</v>
+      </c>
+      <c r="D1" t="str">
+        <v>npwp_16_penyedia</v>
+      </c>
+      <c r="E1" t="str">
+        <v>nilai_negosiasi</v>
+      </c>
+      <c r="F1" t="str">
+        <v>provinsi</v>
+      </c>
+      <c r="G1" t="str">
+        <v>lokasi_pekerjaan</v>
+      </c>
+      <c r="H1" t="str">
+        <v>kd_rup_paket</v>
+      </c>
+      <c r="I1" t="str">
+        <v>pagu</v>
+      </c>
+      <c r="J1" t="str">
+        <v>kd_tender</v>
+      </c>
+      <c r="K1" t="str">
+        <v>kd_penyedia</v>
+      </c>
+      <c r="L1" t="str">
+        <v>tgl_pengumuman_tender</v>
+      </c>
+      <c r="M1" t="str">
         <v>nilai_pdn_kontrak</v>
       </c>
-      <c r="B1" t="str">
-        <v>kd_tender</v>
-      </c>
-      <c r="C1" t="str">
+      <c r="N1" t="str">
+        <v>kabkota</v>
+      </c>
+      <c r="O1" t="str">
+        <v>kd_lpse</v>
+      </c>
+      <c r="P1" t="str">
+        <v>kd_satker</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>hps</v>
+      </c>
+      <c r="R1" t="str">
+        <v>kd_paket</v>
+      </c>
+      <c r="S1" t="str">
+        <v>nilai_terkoreksi</v>
+      </c>
+      <c r="T1" t="str">
+        <v>kd_klpd</v>
+      </c>
+      <c r="U1" t="str">
+        <v>jenis_klpd</v>
+      </c>
+      <c r="V1" t="str">
+        <v>nilai_penawaran</v>
+      </c>
+      <c r="W1" t="str">
+        <v>nama_penyedia</v>
+      </c>
+      <c r="X1" t="str">
+        <v>nilai_umk_kontrak</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>nama_klpd</v>
+      </c>
+      <c r="Z1" t="str">
         <v>nama_satker</v>
       </c>
-      <c r="D1" t="str">
-        <v>provinsi</v>
-      </c>
-      <c r="E1" t="str">
-        <v>tahun_anggaran</v>
-      </c>
-      <c r="F1" t="str">
-        <v>kabkota</v>
-      </c>
-      <c r="G1" t="str">
-        <v>kd_klpd</v>
-      </c>
-      <c r="H1" t="str">
-        <v>npwp_16_penyedia</v>
-      </c>
-      <c r="I1" t="str">
-        <v>kd_satker</v>
-      </c>
-      <c r="J1" t="str">
-        <v>nilai_negosiasi</v>
-      </c>
-      <c r="K1" t="str">
-        <v>pagu</v>
-      </c>
-      <c r="L1" t="str">
-        <v>nilai_penawaran</v>
-      </c>
-      <c r="M1" t="str">
-        <v>nilai_umk_kontrak</v>
-      </c>
-      <c r="N1" t="str">
-        <v>psr_id</v>
-      </c>
-      <c r="O1" t="str">
-        <v>kd_rup_paket</v>
-      </c>
-      <c r="P1" t="str">
-        <v>kd_paket</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>kd_lpse</v>
-      </c>
-      <c r="R1" t="str">
-        <v>lokasi_pekerjaan</v>
-      </c>
-      <c r="S1" t="str">
-        <v>nama_klpd</v>
-      </c>
-      <c r="T1" t="str">
-        <v>hps</v>
-      </c>
-      <c r="U1" t="str">
-        <v>kd_penyedia</v>
-      </c>
-      <c r="V1" t="str">
-        <v>nama_penyedia</v>
-      </c>
-      <c r="W1" t="str">
+      <c r="AA1" t="str">
+        <v>tgl_penetapan_pemenang</v>
+      </c>
+      <c r="AB1" t="str">
         <v>npwp_penyedia</v>
-      </c>
-      <c r="X1" t="str">
-        <v>nilai_terkoreksi</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>tgl_penetapan_pemenang</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>tgl_pengumuman_tender</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>jenis_klpd</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>nilai_kontrak</v>
       </c>
       <c r="AC1" t="str">
         <v>last_update_ref</v>
@@ -490,226 +490,226 @@
     </row>
     <row r="2">
       <c r="B2">
+        <v>2026</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Kalimantan Utara</v>
+      </c>
+      <c r="G2" t="str">
+        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
+      </c>
+      <c r="H2" t="str">
+        <v>66390319</v>
+      </c>
+      <c r="I2">
+        <v>108024405000</v>
+      </c>
+      <c r="J2">
         <v>10157189000</v>
       </c>
-      <c r="C2" t="str">
+      <c r="L2" t="str">
+        <v>2026-07-29T00:00:00Z</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Bulungan (Kab.)</v>
+      </c>
+      <c r="O2">
+        <v>194</v>
+      </c>
+      <c r="P2" t="str">
+        <v>626131</v>
+      </c>
+      <c r="Q2">
+        <v>94577629145</v>
+      </c>
+      <c r="R2">
+        <v>10150225000</v>
+      </c>
+      <c r="T2" t="str">
+        <v>K34</v>
+      </c>
+      <c r="U2" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="Z2" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="D2" t="str">
-        <v>Kalimantan Utara</v>
-      </c>
-      <c r="E2">
-        <v>2026</v>
-      </c>
-      <c r="F2" t="str">
-        <v>Bulungan (Kab.)</v>
-      </c>
-      <c r="G2" t="str">
-        <v>K34</v>
-      </c>
-      <c r="I2" t="str">
-        <v>626131</v>
-      </c>
-      <c r="K2">
-        <v>108024405000</v>
-      </c>
-      <c r="O2" t="str">
-        <v>66390319</v>
-      </c>
-      <c r="P2">
-        <v>10150225000</v>
-      </c>
-      <c r="Q2">
-        <v>194</v>
-      </c>
-      <c r="R2" t="str">
-        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
-      </c>
-      <c r="S2" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="T2">
-        <v>94577629145</v>
-      </c>
-      <c r="Y2" t="str">
+      <c r="AA2" t="str">
         <v>2026-09-03T00:00:00Z</v>
       </c>
-      <c r="Z2" t="str">
-        <v>2026-07-29T00:00:00Z</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
       <c r="AC2" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.HUp3KgHOoKslxwmw.dyydQzJpCL9A1UM6coKqEu_vHnlSyJvCVHx3PZKM-ts</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.K1igx_n_1BGp5LJ7.S1BdIdzPDVbI_5BoRwTAjlUZo0eq2lEwLzmuesfpV_Y</v>
       </c>
     </row>
     <row r="3">
       <c r="B3">
+        <v>2026</v>
+      </c>
+      <c r="F3" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Jl. Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="H3" t="str">
+        <v>67611590</v>
+      </c>
+      <c r="I3">
+        <v>400000000</v>
+      </c>
+      <c r="J3">
         <v>10159515000</v>
       </c>
-      <c r="C3" t="str">
+      <c r="L3" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="O3">
+        <v>194</v>
+      </c>
+      <c r="P3" t="str">
+        <v>452677</v>
+      </c>
+      <c r="Q3">
+        <v>294600000</v>
+      </c>
+      <c r="R3">
+        <v>10152339000</v>
+      </c>
+      <c r="T3" t="str">
+        <v>K34</v>
+      </c>
+      <c r="U3" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="Z3" t="str">
         <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
-      <c r="D3" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="E3">
-        <v>2026</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="G3" t="str">
-        <v>K34</v>
-      </c>
-      <c r="I3" t="str">
-        <v>452677</v>
-      </c>
-      <c r="K3">
-        <v>400000000</v>
-      </c>
-      <c r="O3" t="str">
-        <v>67611590</v>
-      </c>
-      <c r="P3">
-        <v>10152339000</v>
-      </c>
-      <c r="Q3">
-        <v>194</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Jl. Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="S3" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="T3">
-        <v>294600000</v>
-      </c>
-      <c r="Y3" t="str">
+      <c r="AA3" t="str">
         <v>2026-09-17T00:00:00Z</v>
       </c>
-      <c r="Z3" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
       <c r="AC3" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.HUp3KgHOoKslxwmw.dyydQzJpCL9A1UM6coKqEu_vHnlSyJvCVHx3PZKM-ts</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.K1igx_n_1BGp5LJ7.S1BdIdzPDVbI_5BoRwTAjlUZo0eq2lEwLzmuesfpV_Y</v>
       </c>
     </row>
     <row r="4">
       <c r="B4">
+        <v>2026</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Maluku Utara</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
+      </c>
+      <c r="H4" t="str">
+        <v>66390318</v>
+      </c>
+      <c r="I4">
+        <v>72311690000</v>
+      </c>
+      <c r="J4">
         <v>10158222000</v>
       </c>
-      <c r="C4" t="str">
+      <c r="L4" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Halmahera Selatan (Kab.)</v>
+      </c>
+      <c r="O4">
+        <v>194</v>
+      </c>
+      <c r="P4" t="str">
+        <v>626131</v>
+      </c>
+      <c r="Q4">
+        <v>72210016000</v>
+      </c>
+      <c r="R4">
+        <v>10151157000</v>
+      </c>
+      <c r="T4" t="str">
+        <v>K34</v>
+      </c>
+      <c r="U4" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="Z4" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="D4" t="str">
-        <v>Maluku Utara</v>
-      </c>
-      <c r="E4">
-        <v>2026</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Halmahera Selatan (Kab.)</v>
-      </c>
-      <c r="G4" t="str">
-        <v>K34</v>
-      </c>
-      <c r="I4" t="str">
-        <v>626131</v>
-      </c>
-      <c r="K4">
-        <v>72311690000</v>
-      </c>
-      <c r="O4" t="str">
-        <v>66390318</v>
-      </c>
-      <c r="P4">
-        <v>10151157000</v>
-      </c>
-      <c r="Q4">
-        <v>194</v>
-      </c>
-      <c r="R4" t="str">
-        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
-      </c>
-      <c r="S4" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="T4">
-        <v>72210016000</v>
-      </c>
-      <c r="Y4" t="str">
+      <c r="AA4" t="str">
         <v>2026-09-16T00:00:00Z</v>
       </c>
-      <c r="Z4" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="AA4" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
       <c r="AC4" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.HUp3KgHOoKslxwmw.dyydQzJpCL9A1UM6coKqEu_vHnlSyJvCVHx3PZKM-ts</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.K1igx_n_1BGp5LJ7.S1BdIdzPDVbI_5BoRwTAjlUZo0eq2lEwLzmuesfpV_Y</v>
       </c>
     </row>
     <row r="5">
       <c r="B5">
+        <v>2026</v>
+      </c>
+      <c r="F5" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
+      </c>
+      <c r="H5" t="str">
+        <v>67429813</v>
+      </c>
+      <c r="I5">
+        <v>2300000000</v>
+      </c>
+      <c r="J5">
         <v>10151353000</v>
       </c>
-      <c r="C5" t="str">
+      <c r="L5" t="str">
+        <v>2026-07-22T00:00:00Z</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="O5">
+        <v>194</v>
+      </c>
+      <c r="P5" t="str">
+        <v>626132</v>
+      </c>
+      <c r="Q5">
+        <v>2299921875</v>
+      </c>
+      <c r="R5">
+        <v>10144772000</v>
+      </c>
+      <c r="T5" t="str">
+        <v>K34</v>
+      </c>
+      <c r="U5" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="Z5" t="str">
         <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
       </c>
-      <c r="D5" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="E5">
-        <v>2026</v>
-      </c>
-      <c r="F5" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="G5" t="str">
-        <v>K34</v>
-      </c>
-      <c r="I5" t="str">
-        <v>626132</v>
-      </c>
-      <c r="K5">
-        <v>2300000000</v>
-      </c>
-      <c r="O5" t="str">
-        <v>67429813</v>
-      </c>
-      <c r="P5">
-        <v>10144772000</v>
-      </c>
-      <c r="Q5">
-        <v>194</v>
-      </c>
-      <c r="R5" t="str">
-        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
-      </c>
-      <c r="S5" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="T5">
-        <v>2299921875</v>
-      </c>
-      <c r="Y5" t="str">
-        <v>2026-08-18T00:00:00Z</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>2026-07-22T00:00:00Z</v>
-      </c>
       <c r="AA5" t="str">
-        <v>KEMENTERIAN</v>
+        <v>2026-08-21T00:00:00Z</v>
       </c>
       <c r="AC5" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.HUp3KgHOoKslxwmw.dyydQzJpCL9A1UM6coKqEu_vHnlSyJvCVHx3PZKM-ts</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.K1igx_n_1BGp5LJ7.S1BdIdzPDVbI_5BoRwTAjlUZo0eq2lEwLzmuesfpV_Y</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
+++ b/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
@@ -401,315 +401,315 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>kabkota</v>
+      </c>
+      <c r="B1" t="str">
         <v>psr_id</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
+        <v>kd_satker</v>
+      </c>
+      <c r="D1" t="str">
+        <v>nilai_terkoreksi</v>
+      </c>
+      <c r="E1" t="str">
+        <v>npwp_penyedia</v>
+      </c>
+      <c r="F1" t="str">
+        <v>nilai_kontrak</v>
+      </c>
+      <c r="G1" t="str">
+        <v>nilai_penawaran</v>
+      </c>
+      <c r="H1" t="str">
+        <v>npwp_16_penyedia</v>
+      </c>
+      <c r="I1" t="str">
+        <v>tgl_pengumuman_tender</v>
+      </c>
+      <c r="J1" t="str">
+        <v>kd_lpse</v>
+      </c>
+      <c r="K1" t="str">
+        <v>nama_penyedia</v>
+      </c>
+      <c r="L1" t="str">
+        <v>nilai_pdn_kontrak</v>
+      </c>
+      <c r="M1" t="str">
+        <v>hps</v>
+      </c>
+      <c r="N1" t="str">
+        <v>tgl_penetapan_pemenang</v>
+      </c>
+      <c r="O1" t="str">
+        <v>kd_tender</v>
+      </c>
+      <c r="P1" t="str">
+        <v>kd_penyedia</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>nilai_umk_kontrak</v>
+      </c>
+      <c r="R1" t="str">
+        <v>nilai_negosiasi</v>
+      </c>
+      <c r="S1" t="str">
+        <v>kd_rup_paket</v>
+      </c>
+      <c r="T1" t="str">
+        <v>lokasi_pekerjaan</v>
+      </c>
+      <c r="U1" t="str">
+        <v>nama_klpd</v>
+      </c>
+      <c r="V1" t="str">
+        <v>kd_paket</v>
+      </c>
+      <c r="W1" t="str">
+        <v>kd_klpd</v>
+      </c>
+      <c r="X1" t="str">
+        <v>pagu</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>nama_satker</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>provinsi</v>
+      </c>
+      <c r="AA1" t="str">
         <v>tahun_anggaran</v>
       </c>
-      <c r="C1" t="str">
-        <v>nilai_kontrak</v>
-      </c>
-      <c r="D1" t="str">
-        <v>npwp_16_penyedia</v>
-      </c>
-      <c r="E1" t="str">
-        <v>nilai_negosiasi</v>
-      </c>
-      <c r="F1" t="str">
-        <v>provinsi</v>
-      </c>
-      <c r="G1" t="str">
-        <v>lokasi_pekerjaan</v>
-      </c>
-      <c r="H1" t="str">
-        <v>kd_rup_paket</v>
-      </c>
-      <c r="I1" t="str">
-        <v>pagu</v>
-      </c>
-      <c r="J1" t="str">
-        <v>kd_tender</v>
-      </c>
-      <c r="K1" t="str">
-        <v>kd_penyedia</v>
-      </c>
-      <c r="L1" t="str">
-        <v>tgl_pengumuman_tender</v>
-      </c>
-      <c r="M1" t="str">
-        <v>nilai_pdn_kontrak</v>
-      </c>
-      <c r="N1" t="str">
-        <v>kabkota</v>
-      </c>
-      <c r="O1" t="str">
-        <v>kd_lpse</v>
-      </c>
-      <c r="P1" t="str">
-        <v>kd_satker</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>hps</v>
-      </c>
-      <c r="R1" t="str">
-        <v>kd_paket</v>
-      </c>
-      <c r="S1" t="str">
-        <v>nilai_terkoreksi</v>
-      </c>
-      <c r="T1" t="str">
-        <v>kd_klpd</v>
-      </c>
-      <c r="U1" t="str">
+      <c r="AB1" t="str">
         <v>jenis_klpd</v>
-      </c>
-      <c r="V1" t="str">
-        <v>nilai_penawaran</v>
-      </c>
-      <c r="W1" t="str">
-        <v>nama_penyedia</v>
-      </c>
-      <c r="X1" t="str">
-        <v>nilai_umk_kontrak</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>nama_klpd</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>nama_satker</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>tgl_penetapan_pemenang</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>npwp_penyedia</v>
       </c>
       <c r="AC1" t="str">
         <v>last_update_ref</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2">
+      <c r="A2" t="str">
+        <v>Bulungan (Kab.)</v>
+      </c>
+      <c r="C2" t="str">
+        <v>626131</v>
+      </c>
+      <c r="I2" t="str">
+        <v>2026-07-29T00:00:00Z</v>
+      </c>
+      <c r="J2">
+        <v>194</v>
+      </c>
+      <c r="M2">
+        <v>94577629145</v>
+      </c>
+      <c r="N2" t="str">
+        <v>2026-09-17T00:00:00Z</v>
+      </c>
+      <c r="O2">
+        <v>10157189000</v>
+      </c>
+      <c r="S2" t="str">
+        <v>66390319</v>
+      </c>
+      <c r="T2" t="str">
+        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="V2">
+        <v>10150225000</v>
+      </c>
+      <c r="W2" t="str">
+        <v>K34</v>
+      </c>
+      <c r="X2">
+        <v>108024405000</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Kalimantan Utara</v>
+      </c>
+      <c r="AA2">
         <v>2026</v>
       </c>
-      <c r="F2" t="str">
-        <v>Kalimantan Utara</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
-      </c>
-      <c r="H2" t="str">
-        <v>66390319</v>
-      </c>
-      <c r="I2">
-        <v>108024405000</v>
-      </c>
-      <c r="J2">
-        <v>10157189000</v>
-      </c>
-      <c r="L2" t="str">
-        <v>2026-07-29T00:00:00Z</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Bulungan (Kab.)</v>
-      </c>
-      <c r="O2">
-        <v>194</v>
-      </c>
-      <c r="P2" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Q2">
-        <v>94577629145</v>
-      </c>
-      <c r="R2">
-        <v>10150225000</v>
-      </c>
-      <c r="T2" t="str">
-        <v>K34</v>
-      </c>
-      <c r="U2" t="str">
+      <c r="AB2" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="Y2" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>2026-09-03T00:00:00Z</v>
-      </c>
       <c r="AC2" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.K1igx_n_1BGp5LJ7.S1BdIdzPDVbI_5BoRwTAjlUZo0eq2lEwLzmuesfpV_Y</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.spw790JVkqpZ2DP_.Olrpwj3_aqYcd8ljKPV4RNIEDuUlJUlZ030Y3vHDOY0</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3">
+      <c r="A3" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="C3" t="str">
+        <v>452677</v>
+      </c>
+      <c r="I3" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="J3">
+        <v>194</v>
+      </c>
+      <c r="M3">
+        <v>294600000</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2026-09-17T00:00:00Z</v>
+      </c>
+      <c r="O3">
+        <v>10159515000</v>
+      </c>
+      <c r="S3" t="str">
+        <v>67611590</v>
+      </c>
+      <c r="T3" t="str">
+        <v>Jl. Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="U3" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="V3">
+        <v>10152339000</v>
+      </c>
+      <c r="W3" t="str">
+        <v>K34</v>
+      </c>
+      <c r="X3">
+        <v>400000000</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="AA3">
         <v>2026</v>
       </c>
-      <c r="F3" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Jl. Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="H3" t="str">
-        <v>67611590</v>
-      </c>
-      <c r="I3">
-        <v>400000000</v>
-      </c>
-      <c r="J3">
-        <v>10159515000</v>
-      </c>
-      <c r="L3" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="O3">
-        <v>194</v>
-      </c>
-      <c r="P3" t="str">
-        <v>452677</v>
-      </c>
-      <c r="Q3">
-        <v>294600000</v>
-      </c>
-      <c r="R3">
-        <v>10152339000</v>
-      </c>
-      <c r="T3" t="str">
-        <v>K34</v>
-      </c>
-      <c r="U3" t="str">
+      <c r="AB3" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="Y3" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>2026-09-17T00:00:00Z</v>
-      </c>
       <c r="AC3" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.K1igx_n_1BGp5LJ7.S1BdIdzPDVbI_5BoRwTAjlUZo0eq2lEwLzmuesfpV_Y</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.spw790JVkqpZ2DP_.Olrpwj3_aqYcd8ljKPV4RNIEDuUlJUlZ030Y3vHDOY0</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4">
+      <c r="A4" t="str">
+        <v>Halmahera Selatan (Kab.)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>626131</v>
+      </c>
+      <c r="I4" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="J4">
+        <v>194</v>
+      </c>
+      <c r="M4">
+        <v>72210016000</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2026-09-16T00:00:00Z</v>
+      </c>
+      <c r="O4">
+        <v>10158222000</v>
+      </c>
+      <c r="S4" t="str">
+        <v>66390318</v>
+      </c>
+      <c r="T4" t="str">
+        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="V4">
+        <v>10151157000</v>
+      </c>
+      <c r="W4" t="str">
+        <v>K34</v>
+      </c>
+      <c r="X4">
+        <v>72311690000</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>Maluku Utara</v>
+      </c>
+      <c r="AA4">
         <v>2026</v>
       </c>
-      <c r="F4" t="str">
-        <v>Maluku Utara</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
-      </c>
-      <c r="H4" t="str">
-        <v>66390318</v>
-      </c>
-      <c r="I4">
-        <v>72311690000</v>
-      </c>
-      <c r="J4">
-        <v>10158222000</v>
-      </c>
-      <c r="L4" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="N4" t="str">
-        <v>Halmahera Selatan (Kab.)</v>
-      </c>
-      <c r="O4">
-        <v>194</v>
-      </c>
-      <c r="P4" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Q4">
-        <v>72210016000</v>
-      </c>
-      <c r="R4">
-        <v>10151157000</v>
-      </c>
-      <c r="T4" t="str">
-        <v>K34</v>
-      </c>
-      <c r="U4" t="str">
+      <c r="AB4" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="Y4" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="Z4" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="AA4" t="str">
-        <v>2026-09-16T00:00:00Z</v>
-      </c>
       <c r="AC4" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.K1igx_n_1BGp5LJ7.S1BdIdzPDVbI_5BoRwTAjlUZo0eq2lEwLzmuesfpV_Y</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.spw790JVkqpZ2DP_.Olrpwj3_aqYcd8ljKPV4RNIEDuUlJUlZ030Y3vHDOY0</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5">
+      <c r="A5" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="C5" t="str">
+        <v>626132</v>
+      </c>
+      <c r="I5" t="str">
+        <v>2026-07-22T00:00:00Z</v>
+      </c>
+      <c r="J5">
+        <v>194</v>
+      </c>
+      <c r="M5">
+        <v>2299921875</v>
+      </c>
+      <c r="N5" t="str">
+        <v>2026-08-21T00:00:00Z</v>
+      </c>
+      <c r="O5">
+        <v>10151353000</v>
+      </c>
+      <c r="S5" t="str">
+        <v>67429813</v>
+      </c>
+      <c r="T5" t="str">
+        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
+      </c>
+      <c r="U5" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="V5">
+        <v>10144772000</v>
+      </c>
+      <c r="W5" t="str">
+        <v>K34</v>
+      </c>
+      <c r="X5">
+        <v>2300000000</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="AA5">
         <v>2026</v>
       </c>
-      <c r="F5" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
-      </c>
-      <c r="H5" t="str">
-        <v>67429813</v>
-      </c>
-      <c r="I5">
-        <v>2300000000</v>
-      </c>
-      <c r="J5">
-        <v>10151353000</v>
-      </c>
-      <c r="L5" t="str">
-        <v>2026-07-22T00:00:00Z</v>
-      </c>
-      <c r="N5" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="O5">
-        <v>194</v>
-      </c>
-      <c r="P5" t="str">
-        <v>626132</v>
-      </c>
-      <c r="Q5">
-        <v>2299921875</v>
-      </c>
-      <c r="R5">
-        <v>10144772000</v>
-      </c>
-      <c r="T5" t="str">
-        <v>K34</v>
-      </c>
-      <c r="U5" t="str">
+      <c r="AB5" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="Y5" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
       <c r="AC5" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.K1igx_n_1BGp5LJ7.S1BdIdzPDVbI_5BoRwTAjlUZo0eq2lEwLzmuesfpV_Y</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.spw790JVkqpZ2DP_.Olrpwj3_aqYcd8ljKPV4RNIEDuUlJUlZ030Y3vHDOY0</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
+++ b/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
@@ -397,89 +397,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>nilai_umk_kontrak</v>
+      </c>
+      <c r="B1" t="str">
+        <v>tgl_pengumuman_tender</v>
+      </c>
+      <c r="C1" t="str">
+        <v>kd_rup_paket</v>
+      </c>
+      <c r="D1" t="str">
+        <v>hps</v>
+      </c>
+      <c r="E1" t="str">
+        <v>kd_klpd</v>
+      </c>
+      <c r="F1" t="str">
+        <v>provinsi</v>
+      </c>
+      <c r="G1" t="str">
+        <v>nilai_kontrak</v>
+      </c>
+      <c r="H1" t="str">
+        <v>kd_tender</v>
+      </c>
+      <c r="I1" t="str">
+        <v>nilai_negosiasi</v>
+      </c>
+      <c r="J1" t="str">
         <v>kabkota</v>
       </c>
-      <c r="B1" t="str">
-        <v>psr_id</v>
-      </c>
-      <c r="C1" t="str">
-        <v>kd_satker</v>
-      </c>
-      <c r="D1" t="str">
-        <v>nilai_terkoreksi</v>
-      </c>
-      <c r="E1" t="str">
-        <v>npwp_penyedia</v>
-      </c>
-      <c r="F1" t="str">
-        <v>nilai_kontrak</v>
-      </c>
-      <c r="G1" t="str">
+      <c r="K1" t="str">
+        <v>nama_klpd</v>
+      </c>
+      <c r="L1" t="str">
         <v>nilai_penawaran</v>
       </c>
-      <c r="H1" t="str">
-        <v>npwp_16_penyedia</v>
-      </c>
-      <c r="I1" t="str">
-        <v>tgl_pengumuman_tender</v>
-      </c>
-      <c r="J1" t="str">
-        <v>kd_lpse</v>
-      </c>
-      <c r="K1" t="str">
-        <v>nama_penyedia</v>
-      </c>
-      <c r="L1" t="str">
-        <v>nilai_pdn_kontrak</v>
-      </c>
       <c r="M1" t="str">
-        <v>hps</v>
+        <v>kd_paket</v>
       </c>
       <c r="N1" t="str">
         <v>tgl_penetapan_pemenang</v>
       </c>
       <c r="O1" t="str">
-        <v>kd_tender</v>
+        <v>lokasi_pekerjaan</v>
       </c>
       <c r="P1" t="str">
+        <v>tahun_anggaran</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>psr_id</v>
+      </c>
+      <c r="R1" t="str">
+        <v>nama_satker</v>
+      </c>
+      <c r="S1" t="str">
+        <v>nilai_terkoreksi</v>
+      </c>
+      <c r="T1" t="str">
+        <v>kd_satker</v>
+      </c>
+      <c r="U1" t="str">
         <v>kd_penyedia</v>
       </c>
-      <c r="Q1" t="str">
-        <v>nilai_umk_kontrak</v>
-      </c>
-      <c r="R1" t="str">
-        <v>nilai_negosiasi</v>
-      </c>
-      <c r="S1" t="str">
-        <v>kd_rup_paket</v>
-      </c>
-      <c r="T1" t="str">
-        <v>lokasi_pekerjaan</v>
-      </c>
-      <c r="U1" t="str">
-        <v>nama_klpd</v>
-      </c>
       <c r="V1" t="str">
-        <v>kd_paket</v>
+        <v>nama_penyedia</v>
       </c>
       <c r="W1" t="str">
-        <v>kd_klpd</v>
+        <v>nilai_pdn_kontrak</v>
       </c>
       <c r="X1" t="str">
+        <v>npwp_16_penyedia</v>
+      </c>
+      <c r="Y1" t="str">
         <v>pagu</v>
       </c>
-      <c r="Y1" t="str">
-        <v>nama_satker</v>
-      </c>
       <c r="Z1" t="str">
-        <v>provinsi</v>
+        <v>npwp_penyedia</v>
       </c>
       <c r="AA1" t="str">
-        <v>tahun_anggaran</v>
+        <v>kd_lpse</v>
       </c>
       <c r="AB1" t="str">
         <v>jenis_klpd</v>
@@ -489,232 +489,400 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
-        <v>Bulungan (Kab.)</v>
+      <c r="B2" t="str">
+        <v>2026-08-21T00:00:00Z</v>
       </c>
       <c r="C2" t="str">
+        <v>66390312</v>
+      </c>
+      <c r="D2">
+        <v>51439625000</v>
+      </c>
+      <c r="E2" t="str">
+        <v>K34</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Bengkulu</v>
+      </c>
+      <c r="H2">
+        <v>10159959000</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Bengkulu (Kota)</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="M2">
+        <v>10152741000</v>
+      </c>
+      <c r="N2" t="str">
+        <v>2026-10-01T00:00:00Z</v>
+      </c>
+      <c r="O2" t="str">
+        <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
+      </c>
+      <c r="P2">
+        <v>2026</v>
+      </c>
+      <c r="R2" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="T2" t="str">
         <v>626131</v>
       </c>
-      <c r="I2" t="str">
-        <v>2026-07-29T00:00:00Z</v>
-      </c>
-      <c r="J2">
+      <c r="Y2">
+        <v>63441052000</v>
+      </c>
+      <c r="AA2">
         <v>194</v>
-      </c>
-      <c r="M2">
-        <v>94577629145</v>
-      </c>
-      <c r="N2" t="str">
-        <v>2026-09-17T00:00:00Z</v>
-      </c>
-      <c r="O2">
-        <v>10157189000</v>
-      </c>
-      <c r="S2" t="str">
-        <v>66390319</v>
-      </c>
-      <c r="T2" t="str">
-        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
-      </c>
-      <c r="U2" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="V2">
-        <v>10150225000</v>
-      </c>
-      <c r="W2" t="str">
-        <v>K34</v>
-      </c>
-      <c r="X2">
-        <v>108024405000</v>
-      </c>
-      <c r="Y2" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="Z2" t="str">
-        <v>Kalimantan Utara</v>
-      </c>
-      <c r="AA2">
-        <v>2026</v>
       </c>
       <c r="AB2" t="str">
         <v>KEMENTERIAN</v>
       </c>
       <c r="AC2" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.spw790JVkqpZ2DP_.Olrpwj3_aqYcd8ljKPV4RNIEDuUlJUlZ030Y3vHDOY0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>Jakarta Selatan (Kota)</v>
+      <c r="B3" t="str">
+        <v>2026-07-29T00:00:00Z</v>
       </c>
       <c r="C3" t="str">
-        <v>452677</v>
-      </c>
-      <c r="I3" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="J3">
-        <v>194</v>
+        <v>66390319</v>
+      </c>
+      <c r="D3">
+        <v>94577629145</v>
+      </c>
+      <c r="E3" t="str">
+        <v>K34</v>
+      </c>
+      <c r="F3" t="str">
+        <v>Kalimantan Utara</v>
+      </c>
+      <c r="H3">
+        <v>10157189000</v>
+      </c>
+      <c r="J3" t="str">
+        <v>Bulungan (Kab.)</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="M3">
-        <v>294600000</v>
+        <v>10150225000</v>
       </c>
       <c r="N3" t="str">
         <v>2026-09-17T00:00:00Z</v>
       </c>
-      <c r="O3">
-        <v>10159515000</v>
-      </c>
-      <c r="S3" t="str">
-        <v>67611590</v>
+      <c r="O3" t="str">
+        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
+      </c>
+      <c r="P3">
+        <v>2026</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
       <c r="T3" t="str">
-        <v>Jl. Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="U3" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="V3">
-        <v>10152339000</v>
-      </c>
-      <c r="W3" t="str">
-        <v>K34</v>
-      </c>
-      <c r="X3">
-        <v>400000000</v>
-      </c>
-      <c r="Y3" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="Z3" t="str">
-        <v>DKI Jakarta</v>
+        <v>626131</v>
+      </c>
+      <c r="Y3">
+        <v>108024405000</v>
       </c>
       <c r="AA3">
-        <v>2026</v>
+        <v>194</v>
       </c>
       <c r="AB3" t="str">
         <v>KEMENTERIAN</v>
       </c>
       <c r="AC3" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.spw790JVkqpZ2DP_.Olrpwj3_aqYcd8ljKPV4RNIEDuUlJUlZ030Y3vHDOY0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
-        <v>Halmahera Selatan (Kab.)</v>
+      <c r="B4" t="str">
+        <v>2026-08-05T00:00:00Z</v>
       </c>
       <c r="C4" t="str">
-        <v>626131</v>
-      </c>
-      <c r="I4" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="J4">
+        <v>67611590</v>
+      </c>
+      <c r="D4">
+        <v>294600000</v>
+      </c>
+      <c r="E4" t="str">
+        <v>K34</v>
+      </c>
+      <c r="F4" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="H4">
+        <v>10159515000</v>
+      </c>
+      <c r="J4" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="K4" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="M4">
+        <v>10152339000</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2026-09-17T00:00:00Z</v>
+      </c>
+      <c r="O4" t="str">
+        <v>Jl. Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="P4">
+        <v>2026</v>
+      </c>
+      <c r="R4" t="str">
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      </c>
+      <c r="T4" t="str">
+        <v>452677</v>
+      </c>
+      <c r="Y4">
+        <v>400000000</v>
+      </c>
+      <c r="AA4">
         <v>194</v>
-      </c>
-      <c r="M4">
-        <v>72210016000</v>
-      </c>
-      <c r="N4" t="str">
-        <v>2026-09-16T00:00:00Z</v>
-      </c>
-      <c r="O4">
-        <v>10158222000</v>
-      </c>
-      <c r="S4" t="str">
-        <v>66390318</v>
-      </c>
-      <c r="T4" t="str">
-        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
-      </c>
-      <c r="U4" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="V4">
-        <v>10151157000</v>
-      </c>
-      <c r="W4" t="str">
-        <v>K34</v>
-      </c>
-      <c r="X4">
-        <v>72311690000</v>
-      </c>
-      <c r="Y4" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="Z4" t="str">
-        <v>Maluku Utara</v>
-      </c>
-      <c r="AA4">
-        <v>2026</v>
       </c>
       <c r="AB4" t="str">
         <v>KEMENTERIAN</v>
       </c>
       <c r="AC4" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.spw790JVkqpZ2DP_.Olrpwj3_aqYcd8ljKPV4RNIEDuUlJUlZ030Y3vHDOY0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="B5" t="str">
+        <v>2026-08-21T00:00:00Z</v>
+      </c>
+      <c r="C5" t="str">
+        <v>67592003</v>
+      </c>
+      <c r="D5">
+        <v>12677050659</v>
+      </c>
+      <c r="E5" t="str">
+        <v>K34</v>
+      </c>
+      <c r="F5" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="H5">
+        <v>10160960000</v>
+      </c>
+      <c r="J5" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="C5" t="str">
-        <v>626132</v>
-      </c>
-      <c r="I5" t="str">
-        <v>2026-07-22T00:00:00Z</v>
-      </c>
-      <c r="J5">
+      <c r="K5" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="M5">
+        <v>10153666000</v>
+      </c>
+      <c r="N5" t="str">
+        <v>2026-10-07T00:00:00Z</v>
+      </c>
+      <c r="O5" t="str">
+        <v>Jl Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="P5">
+        <v>2026</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      </c>
+      <c r="T5" t="str">
+        <v>452677</v>
+      </c>
+      <c r="Y5">
+        <v>14699105000</v>
+      </c>
+      <c r="AA5">
         <v>194</v>
-      </c>
-      <c r="M5">
-        <v>2299921875</v>
-      </c>
-      <c r="N5" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
-      <c r="O5">
-        <v>10151353000</v>
-      </c>
-      <c r="S5" t="str">
-        <v>67429813</v>
-      </c>
-      <c r="T5" t="str">
-        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
-      </c>
-      <c r="U5" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="V5">
-        <v>10144772000</v>
-      </c>
-      <c r="W5" t="str">
-        <v>K34</v>
-      </c>
-      <c r="X5">
-        <v>2300000000</v>
-      </c>
-      <c r="Y5" t="str">
-        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
-      </c>
-      <c r="Z5" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="AA5">
-        <v>2026</v>
       </c>
       <c r="AB5" t="str">
         <v>KEMENTERIAN</v>
       </c>
       <c r="AC5" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.spw790JVkqpZ2DP_.Olrpwj3_aqYcd8ljKPV4RNIEDuUlJUlZ030Y3vHDOY0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="str">
+        <v>2026-08-20T00:00:00Z</v>
+      </c>
+      <c r="C6" t="str">
+        <v>67538462</v>
+      </c>
+      <c r="D6">
+        <v>646650000</v>
+      </c>
+      <c r="E6" t="str">
+        <v>K34</v>
+      </c>
+      <c r="F6" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="H6">
+        <v>10162858000</v>
+      </c>
+      <c r="J6" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="K6" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="M6">
+        <v>10155417000</v>
+      </c>
+      <c r="N6" t="str">
+        <v>2026-09-23T00:00:00Z</v>
+      </c>
+      <c r="O6" t="str">
+        <v>Jl Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="P6">
+        <v>2026</v>
+      </c>
+      <c r="R6" t="str">
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      </c>
+      <c r="T6" t="str">
+        <v>452677</v>
+      </c>
+      <c r="Y6">
+        <v>654750000</v>
+      </c>
+      <c r="AA6">
+        <v>194</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="AC6" t="str">
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="C7" t="str">
+        <v>66390318</v>
+      </c>
+      <c r="D7">
+        <v>72210016000</v>
+      </c>
+      <c r="E7" t="str">
+        <v>K34</v>
+      </c>
+      <c r="F7" t="str">
+        <v>Maluku Utara</v>
+      </c>
+      <c r="H7">
+        <v>10158222000</v>
+      </c>
+      <c r="J7" t="str">
+        <v>Halmahera Selatan (Kab.)</v>
+      </c>
+      <c r="K7" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="M7">
+        <v>10151157000</v>
+      </c>
+      <c r="N7" t="str">
+        <v>2026-09-16T00:00:00Z</v>
+      </c>
+      <c r="O7" t="str">
+        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
+      </c>
+      <c r="P7">
+        <v>2026</v>
+      </c>
+      <c r="R7" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="T7" t="str">
+        <v>626131</v>
+      </c>
+      <c r="Y7">
+        <v>72311690000</v>
+      </c>
+      <c r="AA7">
+        <v>194</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="AC7" t="str">
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="str">
+        <v>2026-07-22T00:00:00Z</v>
+      </c>
+      <c r="C8" t="str">
+        <v>67429813</v>
+      </c>
+      <c r="D8">
+        <v>2299921875</v>
+      </c>
+      <c r="E8" t="str">
+        <v>K34</v>
+      </c>
+      <c r="F8" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="H8">
+        <v>10151353000</v>
+      </c>
+      <c r="J8" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="K8" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="M8">
+        <v>10144772000</v>
+      </c>
+      <c r="N8" t="str">
+        <v>2026-08-26T00:00:00Z</v>
+      </c>
+      <c r="O8" t="str">
+        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
+      </c>
+      <c r="P8">
+        <v>2026</v>
+      </c>
+      <c r="R8" t="str">
+        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
+      </c>
+      <c r="T8" t="str">
+        <v>626132</v>
+      </c>
+      <c r="Y8">
+        <v>2300000000</v>
+      </c>
+      <c r="AA8">
+        <v>194</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
+++ b/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
@@ -397,492 +397,436 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>nilai_umk_kontrak</v>
+        <v>nama_penyedia</v>
       </c>
       <c r="B1" t="str">
-        <v>tgl_pengumuman_tender</v>
+        <v>kd_paket</v>
       </c>
       <c r="C1" t="str">
-        <v>kd_rup_paket</v>
+        <v>nilai_kontrak</v>
       </c>
       <c r="D1" t="str">
         <v>hps</v>
       </c>
       <c r="E1" t="str">
-        <v>kd_klpd</v>
+        <v>tgl_pengumuman_tender</v>
       </c>
       <c r="F1" t="str">
         <v>provinsi</v>
       </c>
       <c r="G1" t="str">
-        <v>nilai_kontrak</v>
+        <v>npwp_penyedia</v>
       </c>
       <c r="H1" t="str">
+        <v>nama_satker</v>
+      </c>
+      <c r="I1" t="str">
+        <v>pagu</v>
+      </c>
+      <c r="J1" t="str">
+        <v>kd_rup_paket</v>
+      </c>
+      <c r="K1" t="str">
+        <v>tahun_anggaran</v>
+      </c>
+      <c r="L1" t="str">
+        <v>kd_klpd</v>
+      </c>
+      <c r="M1" t="str">
+        <v>nilai_umk_kontrak</v>
+      </c>
+      <c r="N1" t="str">
+        <v>kabkota</v>
+      </c>
+      <c r="O1" t="str">
         <v>kd_tender</v>
       </c>
-      <c r="I1" t="str">
+      <c r="P1" t="str">
+        <v>lokasi_pekerjaan</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>kd_lpse</v>
+      </c>
+      <c r="R1" t="str">
+        <v>nilai_pdn_kontrak</v>
+      </c>
+      <c r="S1" t="str">
+        <v>npwp_16_penyedia</v>
+      </c>
+      <c r="T1" t="str">
+        <v>jenis_klpd</v>
+      </c>
+      <c r="U1" t="str">
+        <v>kd_satker</v>
+      </c>
+      <c r="V1" t="str">
+        <v>nama_klpd</v>
+      </c>
+      <c r="W1" t="str">
+        <v>tgl_penetapan_pemenang</v>
+      </c>
+      <c r="X1" t="str">
+        <v>kd_penyedia</v>
+      </c>
+      <c r="Y1" t="str">
         <v>nilai_negosiasi</v>
       </c>
-      <c r="J1" t="str">
-        <v>kabkota</v>
-      </c>
-      <c r="K1" t="str">
-        <v>nama_klpd</v>
-      </c>
-      <c r="L1" t="str">
+      <c r="Z1" t="str">
+        <v>nilai_terkoreksi</v>
+      </c>
+      <c r="AA1" t="str">
         <v>nilai_penawaran</v>
       </c>
-      <c r="M1" t="str">
-        <v>kd_paket</v>
-      </c>
-      <c r="N1" t="str">
-        <v>tgl_penetapan_pemenang</v>
-      </c>
-      <c r="O1" t="str">
-        <v>lokasi_pekerjaan</v>
-      </c>
-      <c r="P1" t="str">
-        <v>tahun_anggaran</v>
-      </c>
-      <c r="Q1" t="str">
+      <c r="AB1" t="str">
         <v>psr_id</v>
-      </c>
-      <c r="R1" t="str">
-        <v>nama_satker</v>
-      </c>
-      <c r="S1" t="str">
-        <v>nilai_terkoreksi</v>
-      </c>
-      <c r="T1" t="str">
-        <v>kd_satker</v>
-      </c>
-      <c r="U1" t="str">
-        <v>kd_penyedia</v>
-      </c>
-      <c r="V1" t="str">
-        <v>nama_penyedia</v>
-      </c>
-      <c r="W1" t="str">
-        <v>nilai_pdn_kontrak</v>
-      </c>
-      <c r="X1" t="str">
-        <v>npwp_16_penyedia</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>pagu</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>npwp_penyedia</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>kd_lpse</v>
-      </c>
-      <c r="AB1" t="str">
-        <v>jenis_klpd</v>
       </c>
       <c r="AC1" t="str">
         <v>last_update_ref</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
-      <c r="C2" t="str">
-        <v>66390312</v>
+      <c r="B2">
+        <v>10152741000</v>
       </c>
       <c r="D2">
         <v>51439625000</v>
       </c>
       <c r="E2" t="str">
-        <v>K34</v>
+        <v>2026-08-21T00:00:00Z</v>
       </c>
       <c r="F2" t="str">
         <v>Bengkulu</v>
       </c>
-      <c r="H2">
+      <c r="H2" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="I2">
+        <v>63441052000</v>
+      </c>
+      <c r="J2" t="str">
+        <v>66390312</v>
+      </c>
+      <c r="K2">
+        <v>2026</v>
+      </c>
+      <c r="L2" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Bengkulu (Kota)</v>
+      </c>
+      <c r="O2">
         <v>10159959000</v>
       </c>
-      <c r="J2" t="str">
-        <v>Bengkulu (Kota)</v>
-      </c>
-      <c r="K2" t="str">
+      <c r="P2" t="str">
+        <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
+      </c>
+      <c r="Q2">
+        <v>194</v>
+      </c>
+      <c r="T2" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="U2" t="str">
+        <v>626131</v>
+      </c>
+      <c r="V2" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M2">
-        <v>10152741000</v>
-      </c>
-      <c r="N2" t="str">
+      <c r="W2" t="str">
         <v>2026-10-01T00:00:00Z</v>
       </c>
-      <c r="O2" t="str">
-        <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
-      </c>
-      <c r="P2">
-        <v>2026</v>
-      </c>
-      <c r="R2" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="T2" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Y2">
-        <v>63441052000</v>
-      </c>
-      <c r="AA2">
-        <v>194</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
       <c r="AC2" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.p0ZzV3QVc-16QjBE.0yNacvEeYvJ9--dFvzWKvXFxcr680TtcS9Z7azM4J0Q</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="str">
-        <v>2026-07-29T00:00:00Z</v>
-      </c>
-      <c r="C3" t="str">
-        <v>66390319</v>
+      <c r="B3">
+        <v>10150225000</v>
       </c>
       <c r="D3">
         <v>94577629145</v>
       </c>
       <c r="E3" t="str">
-        <v>K34</v>
+        <v>2026-07-29T00:00:00Z</v>
       </c>
       <c r="F3" t="str">
         <v>Kalimantan Utara</v>
       </c>
-      <c r="H3">
+      <c r="H3" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="I3">
+        <v>108024405000</v>
+      </c>
+      <c r="J3" t="str">
+        <v>66390319</v>
+      </c>
+      <c r="K3">
+        <v>2026</v>
+      </c>
+      <c r="L3" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Bulungan (Kab.)</v>
+      </c>
+      <c r="O3">
         <v>10157189000</v>
       </c>
-      <c r="J3" t="str">
-        <v>Bulungan (Kab.)</v>
-      </c>
-      <c r="K3" t="str">
+      <c r="P3" t="str">
+        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
+      </c>
+      <c r="Q3">
+        <v>194</v>
+      </c>
+      <c r="T3" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="U3" t="str">
+        <v>626131</v>
+      </c>
+      <c r="V3" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M3">
-        <v>10150225000</v>
-      </c>
-      <c r="N3" t="str">
+      <c r="W3" t="str">
         <v>2026-09-17T00:00:00Z</v>
       </c>
-      <c r="O3" t="str">
-        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
-      </c>
-      <c r="P3">
-        <v>2026</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="T3" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Y3">
-        <v>108024405000</v>
-      </c>
-      <c r="AA3">
-        <v>194</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
       <c r="AC3" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.p0ZzV3QVc-16QjBE.0yNacvEeYvJ9--dFvzWKvXFxcr680TtcS9Z7azM4J0Q</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="C4" t="str">
-        <v>67611590</v>
+      <c r="B4">
+        <v>10152339000</v>
       </c>
       <c r="D4">
         <v>294600000</v>
       </c>
       <c r="E4" t="str">
-        <v>K34</v>
+        <v>2026-08-05T00:00:00Z</v>
       </c>
       <c r="F4" t="str">
         <v>DKI Jakarta</v>
       </c>
-      <c r="H4">
+      <c r="H4" t="str">
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      </c>
+      <c r="I4">
+        <v>400000000</v>
+      </c>
+      <c r="J4" t="str">
+        <v>67611590</v>
+      </c>
+      <c r="K4">
+        <v>2026</v>
+      </c>
+      <c r="L4" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="O4">
         <v>10159515000</v>
       </c>
-      <c r="J4" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="K4" t="str">
+      <c r="P4" t="str">
+        <v>Jl. Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="Q4">
+        <v>194</v>
+      </c>
+      <c r="T4" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="U4" t="str">
+        <v>452677</v>
+      </c>
+      <c r="V4" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M4">
-        <v>10152339000</v>
-      </c>
-      <c r="N4" t="str">
+      <c r="W4" t="str">
         <v>2026-09-17T00:00:00Z</v>
       </c>
-      <c r="O4" t="str">
-        <v>Jl. Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="P4">
-        <v>2026</v>
-      </c>
-      <c r="R4" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="T4" t="str">
-        <v>452677</v>
-      </c>
-      <c r="Y4">
-        <v>400000000</v>
-      </c>
-      <c r="AA4">
-        <v>194</v>
-      </c>
-      <c r="AB4" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
       <c r="AC4" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.p0ZzV3QVc-16QjBE.0yNacvEeYvJ9--dFvzWKvXFxcr680TtcS9Z7azM4J0Q</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
-      <c r="C5" t="str">
-        <v>67592003</v>
+      <c r="B5">
+        <v>10153666000</v>
       </c>
       <c r="D5">
         <v>12677050659</v>
       </c>
       <c r="E5" t="str">
-        <v>K34</v>
+        <v>2026-08-21T00:00:00Z</v>
       </c>
       <c r="F5" t="str">
         <v>DKI Jakarta</v>
       </c>
-      <c r="H5">
+      <c r="H5" t="str">
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      </c>
+      <c r="I5">
+        <v>14699105000</v>
+      </c>
+      <c r="J5" t="str">
+        <v>67592003</v>
+      </c>
+      <c r="K5">
+        <v>2026</v>
+      </c>
+      <c r="L5" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="O5">
         <v>10160960000</v>
       </c>
-      <c r="J5" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="K5" t="str">
+      <c r="P5" t="str">
+        <v>Jl Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="Q5">
+        <v>194</v>
+      </c>
+      <c r="T5" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="U5" t="str">
+        <v>452677</v>
+      </c>
+      <c r="V5" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M5">
-        <v>10153666000</v>
-      </c>
-      <c r="N5" t="str">
+      <c r="W5" t="str">
         <v>2026-10-07T00:00:00Z</v>
       </c>
-      <c r="O5" t="str">
-        <v>Jl Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="P5">
-        <v>2026</v>
-      </c>
-      <c r="R5" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="T5" t="str">
-        <v>452677</v>
-      </c>
-      <c r="Y5">
-        <v>14699105000</v>
-      </c>
-      <c r="AA5">
-        <v>194</v>
-      </c>
-      <c r="AB5" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
       <c r="AC5" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.p0ZzV3QVc-16QjBE.0yNacvEeYvJ9--dFvzWKvXFxcr680TtcS9Z7azM4J0Q</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="str">
-        <v>2026-08-20T00:00:00Z</v>
-      </c>
-      <c r="C6" t="str">
-        <v>67538462</v>
+      <c r="B6">
+        <v>10151157000</v>
       </c>
       <c r="D6">
-        <v>646650000</v>
+        <v>72210016000</v>
       </c>
       <c r="E6" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="F6" t="str">
+        <v>Maluku Utara</v>
+      </c>
+      <c r="H6" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="I6">
+        <v>72311690000</v>
+      </c>
+      <c r="J6" t="str">
+        <v>66390318</v>
+      </c>
+      <c r="K6">
+        <v>2026</v>
+      </c>
+      <c r="L6" t="str">
         <v>K34</v>
       </c>
-      <c r="F6" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="H6">
-        <v>10162858000</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="K6" t="str">
+      <c r="N6" t="str">
+        <v>Halmahera Selatan (Kab.)</v>
+      </c>
+      <c r="O6">
+        <v>10158222000</v>
+      </c>
+      <c r="P6" t="str">
+        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
+      </c>
+      <c r="Q6">
+        <v>194</v>
+      </c>
+      <c r="T6" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="U6" t="str">
+        <v>626131</v>
+      </c>
+      <c r="V6" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M6">
-        <v>10155417000</v>
-      </c>
-      <c r="N6" t="str">
-        <v>2026-09-23T00:00:00Z</v>
-      </c>
-      <c r="O6" t="str">
-        <v>Jl Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="P6">
-        <v>2026</v>
-      </c>
-      <c r="R6" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="T6" t="str">
-        <v>452677</v>
-      </c>
-      <c r="Y6">
-        <v>654750000</v>
-      </c>
-      <c r="AA6">
-        <v>194</v>
-      </c>
-      <c r="AB6" t="str">
-        <v>KEMENTERIAN</v>
+      <c r="W6" t="str">
+        <v>2026-09-16T00:00:00Z</v>
       </c>
       <c r="AC6" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.p0ZzV3QVc-16QjBE.0yNacvEeYvJ9--dFvzWKvXFxcr680TtcS9Z7azM4J0Q</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="C7" t="str">
-        <v>66390318</v>
+      <c r="B7">
+        <v>10144772000</v>
       </c>
       <c r="D7">
-        <v>72210016000</v>
+        <v>2299921875</v>
       </c>
       <c r="E7" t="str">
+        <v>2026-07-22T00:00:00Z</v>
+      </c>
+      <c r="F7" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="H7" t="str">
+        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
+      </c>
+      <c r="I7">
+        <v>2300000000</v>
+      </c>
+      <c r="J7" t="str">
+        <v>67429813</v>
+      </c>
+      <c r="K7">
+        <v>2026</v>
+      </c>
+      <c r="L7" t="str">
         <v>K34</v>
       </c>
-      <c r="F7" t="str">
-        <v>Maluku Utara</v>
-      </c>
-      <c r="H7">
-        <v>10158222000</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Halmahera Selatan (Kab.)</v>
-      </c>
-      <c r="K7" t="str">
+      <c r="N7" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="O7">
+        <v>10151353000</v>
+      </c>
+      <c r="P7" t="str">
+        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
+      </c>
+      <c r="Q7">
+        <v>194</v>
+      </c>
+      <c r="T7" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="U7" t="str">
+        <v>626132</v>
+      </c>
+      <c r="V7" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M7">
-        <v>10151157000</v>
-      </c>
-      <c r="N7" t="str">
-        <v>2026-09-16T00:00:00Z</v>
-      </c>
-      <c r="O7" t="str">
-        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
-      </c>
-      <c r="P7">
-        <v>2026</v>
-      </c>
-      <c r="R7" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="T7" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Y7">
-        <v>72311690000</v>
-      </c>
-      <c r="AA7">
-        <v>194</v>
-      </c>
-      <c r="AB7" t="str">
-        <v>KEMENTERIAN</v>
+      <c r="W7" t="str">
+        <v>2026-08-26T00:00:00Z</v>
       </c>
       <c r="AC7" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" t="str">
-        <v>2026-07-22T00:00:00Z</v>
-      </c>
-      <c r="C8" t="str">
-        <v>67429813</v>
-      </c>
-      <c r="D8">
-        <v>2299921875</v>
-      </c>
-      <c r="E8" t="str">
-        <v>K34</v>
-      </c>
-      <c r="F8" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="H8">
-        <v>10151353000</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="K8" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="M8">
-        <v>10144772000</v>
-      </c>
-      <c r="N8" t="str">
-        <v>2026-08-26T00:00:00Z</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
-      </c>
-      <c r="P8">
-        <v>2026</v>
-      </c>
-      <c r="R8" t="str">
-        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
-      </c>
-      <c r="T8" t="str">
-        <v>626132</v>
-      </c>
-      <c r="Y8">
-        <v>2300000000</v>
-      </c>
-      <c r="AA8">
-        <v>194</v>
-      </c>
-      <c r="AB8" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="AC8" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.p0ZzV3QVc-16QjBE.0yNacvEeYvJ9--dFvzWKvXFxcr680TtcS9Z7azM4J0Q</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
+++ b/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
@@ -401,483 +401,510 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>nilai_umk_kontrak</v>
+        <v>lokasi_pekerjaan</v>
       </c>
       <c r="B1" t="str">
+        <v>nama_satker</v>
+      </c>
+      <c r="C1" t="str">
+        <v>npwp_penyedia</v>
+      </c>
+      <c r="D1" t="str">
+        <v>pagu</v>
+      </c>
+      <c r="E1" t="str">
+        <v>jenis_klpd</v>
+      </c>
+      <c r="F1" t="str">
+        <v>nilai_terkoreksi</v>
+      </c>
+      <c r="G1" t="str">
         <v>tgl_pengumuman_tender</v>
       </c>
-      <c r="C1" t="str">
-        <v>kd_rup_paket</v>
-      </c>
-      <c r="D1" t="str">
-        <v>hps</v>
-      </c>
-      <c r="E1" t="str">
+      <c r="H1" t="str">
+        <v>kd_penyedia</v>
+      </c>
+      <c r="I1" t="str">
+        <v>nama_penyedia</v>
+      </c>
+      <c r="J1" t="str">
+        <v>nilai_pdn_kontrak</v>
+      </c>
+      <c r="K1" t="str">
         <v>kd_klpd</v>
       </c>
-      <c r="F1" t="str">
-        <v>provinsi</v>
-      </c>
-      <c r="G1" t="str">
-        <v>nilai_kontrak</v>
-      </c>
-      <c r="H1" t="str">
-        <v>kd_tender</v>
-      </c>
-      <c r="I1" t="str">
+      <c r="L1" t="str">
+        <v>kabkota</v>
+      </c>
+      <c r="M1" t="str">
         <v>nilai_negosiasi</v>
-      </c>
-      <c r="J1" t="str">
-        <v>kabkota</v>
-      </c>
-      <c r="K1" t="str">
-        <v>nama_klpd</v>
-      </c>
-      <c r="L1" t="str">
-        <v>nilai_penawaran</v>
-      </c>
-      <c r="M1" t="str">
-        <v>kd_paket</v>
       </c>
       <c r="N1" t="str">
         <v>tgl_penetapan_pemenang</v>
       </c>
       <c r="O1" t="str">
-        <v>lokasi_pekerjaan</v>
+        <v>nilai_penawaran</v>
       </c>
       <c r="P1" t="str">
-        <v>tahun_anggaran</v>
+        <v>nilai_umk_kontrak</v>
       </c>
       <c r="Q1" t="str">
         <v>psr_id</v>
       </c>
       <c r="R1" t="str">
-        <v>nama_satker</v>
+        <v>provinsi</v>
       </c>
       <c r="S1" t="str">
-        <v>nilai_terkoreksi</v>
+        <v>hps</v>
       </c>
       <c r="T1" t="str">
+        <v>nilai_kontrak</v>
+      </c>
+      <c r="U1" t="str">
+        <v>kd_paket</v>
+      </c>
+      <c r="V1" t="str">
+        <v>kd_rup_paket</v>
+      </c>
+      <c r="W1" t="str">
+        <v>npwp_16_penyedia</v>
+      </c>
+      <c r="X1" t="str">
+        <v>tahun_anggaran</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>kd_lpse</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>nama_klpd</v>
+      </c>
+      <c r="AA1" t="str">
         <v>kd_satker</v>
       </c>
-      <c r="U1" t="str">
-        <v>kd_penyedia</v>
-      </c>
-      <c r="V1" t="str">
-        <v>nama_penyedia</v>
-      </c>
-      <c r="W1" t="str">
-        <v>nilai_pdn_kontrak</v>
-      </c>
-      <c r="X1" t="str">
-        <v>npwp_16_penyedia</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>pagu</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>npwp_penyedia</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>kd_lpse</v>
-      </c>
       <c r="AB1" t="str">
-        <v>jenis_klpd</v>
+        <v>kd_tender</v>
       </c>
       <c r="AC1" t="str">
         <v>last_update_ref</v>
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="str">
+        <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
+      </c>
       <c r="B2" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="D2">
+        <v>63441052000</v>
+      </c>
+      <c r="E2" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="G2" t="str">
         <v>2026-08-21T00:00:00Z</v>
       </c>
-      <c r="C2" t="str">
-        <v>66390312</v>
-      </c>
-      <c r="D2">
-        <v>51439625000</v>
-      </c>
-      <c r="E2" t="str">
+      <c r="K2" t="str">
         <v>K34</v>
       </c>
-      <c r="F2" t="str">
-        <v>Bengkulu</v>
-      </c>
-      <c r="H2">
-        <v>10159959000</v>
-      </c>
-      <c r="J2" t="str">
+      <c r="L2" t="str">
         <v>Bengkulu (Kota)</v>
-      </c>
-      <c r="K2" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="M2">
-        <v>10152741000</v>
       </c>
       <c r="N2" t="str">
         <v>2026-10-01T00:00:00Z</v>
       </c>
-      <c r="O2" t="str">
-        <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
-      </c>
-      <c r="P2">
+      <c r="R2" t="str">
+        <v>Bengkulu</v>
+      </c>
+      <c r="S2">
+        <v>51439625000</v>
+      </c>
+      <c r="U2">
+        <v>10152741000</v>
+      </c>
+      <c r="V2" t="str">
+        <v>66390312</v>
+      </c>
+      <c r="X2">
         <v>2026</v>
       </c>
-      <c r="R2" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="T2" t="str">
+      <c r="Y2">
+        <v>194</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="AA2" t="str">
         <v>626131</v>
       </c>
-      <c r="Y2">
-        <v>63441052000</v>
-      </c>
-      <c r="AA2">
-        <v>194</v>
-      </c>
-      <c r="AB2" t="str">
-        <v>KEMENTERIAN</v>
+      <c r="AB2">
+        <v>10159959000</v>
       </c>
       <c r="AC2" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="str">
+        <v>Desa Batu Besar, Kecamatan Nongsa, Kota Batam, Provinsi Kepulauan Riau</v>
+      </c>
       <c r="B3" t="str">
-        <v>2026-07-29T00:00:00Z</v>
-      </c>
-      <c r="C3" t="str">
-        <v>66390319</v>
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
       <c r="D3">
-        <v>94577629145</v>
+        <v>54624000000</v>
       </c>
       <c r="E3" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="G3" t="str">
+        <v>2026-08-28T00:00:00Z</v>
+      </c>
+      <c r="K3" t="str">
         <v>K34</v>
       </c>
-      <c r="F3" t="str">
-        <v>Kalimantan Utara</v>
-      </c>
-      <c r="H3">
-        <v>10157189000</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Bulungan (Kab.)</v>
-      </c>
-      <c r="K3" t="str">
+      <c r="L3" t="str">
+        <v>Batam (Kota)</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2026-10-06T00:00:00Z</v>
+      </c>
+      <c r="R3" t="str">
+        <v>Kepulauan Riau</v>
+      </c>
+      <c r="S3">
+        <v>54472055602.06</v>
+      </c>
+      <c r="U3">
+        <v>10155602000</v>
+      </c>
+      <c r="V3" t="str">
+        <v>66390327</v>
+      </c>
+      <c r="X3">
+        <v>2026</v>
+      </c>
+      <c r="Y3">
+        <v>194</v>
+      </c>
+      <c r="Z3" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M3">
-        <v>10150225000</v>
-      </c>
-      <c r="N3" t="str">
-        <v>2026-09-17T00:00:00Z</v>
-      </c>
-      <c r="O3" t="str">
-        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
-      </c>
-      <c r="P3">
-        <v>2026</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="T3" t="str">
+      <c r="AA3" t="str">
         <v>626131</v>
       </c>
-      <c r="Y3">
-        <v>108024405000</v>
-      </c>
-      <c r="AA3">
-        <v>194</v>
-      </c>
-      <c r="AB3" t="str">
-        <v>KEMENTERIAN</v>
+      <c r="AB3">
+        <v>10163085000</v>
       </c>
       <c r="AC3" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="str">
+        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
+      </c>
       <c r="B4" t="str">
-        <v>2026-08-05T00:00:00Z</v>
+        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
       </c>
       <c r="C4" t="str">
-        <v>67611590</v>
+        <v>01.308.279.7-001.000</v>
       </c>
       <c r="D4">
-        <v>294600000</v>
+        <v>2300000000</v>
       </c>
       <c r="E4" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="F4">
+        <v>2089050250</v>
+      </c>
+      <c r="G4" t="str">
+        <v>2026-07-22T00:00:00Z</v>
+      </c>
+      <c r="H4">
+        <v>712065</v>
+      </c>
+      <c r="I4" t="str">
+        <v>PT INERSIA AMPAK ENGINEERS</v>
+      </c>
+      <c r="K4" t="str">
         <v>K34</v>
       </c>
-      <c r="F4" t="str">
+      <c r="L4" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="M4">
+        <v>2089050250</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2026-08-27T00:00:00Z</v>
+      </c>
+      <c r="O4">
+        <v>2089050250</v>
+      </c>
+      <c r="Q4">
+        <v>11760143000</v>
+      </c>
+      <c r="R4" t="str">
         <v>DKI Jakarta</v>
       </c>
-      <c r="H4">
-        <v>10159515000</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="K4" t="str">
+      <c r="S4">
+        <v>2299921875</v>
+      </c>
+      <c r="T4">
+        <v>2089050250</v>
+      </c>
+      <c r="U4">
+        <v>10144772000</v>
+      </c>
+      <c r="V4" t="str">
+        <v>67429813</v>
+      </c>
+      <c r="W4" t="str">
+        <v>0013082797001000</v>
+      </c>
+      <c r="X4">
+        <v>2026</v>
+      </c>
+      <c r="Y4">
+        <v>194</v>
+      </c>
+      <c r="Z4" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M4">
-        <v>10152339000</v>
-      </c>
-      <c r="N4" t="str">
-        <v>2026-09-17T00:00:00Z</v>
-      </c>
-      <c r="O4" t="str">
-        <v>Jl. Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="P4">
-        <v>2026</v>
-      </c>
-      <c r="R4" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="T4" t="str">
-        <v>452677</v>
-      </c>
-      <c r="Y4">
-        <v>400000000</v>
-      </c>
-      <c r="AA4">
-        <v>194</v>
-      </c>
-      <c r="AB4" t="str">
-        <v>KEMENTERIAN</v>
+      <c r="AA4" t="str">
+        <v>626132</v>
+      </c>
+      <c r="AB4">
+        <v>10151353000</v>
       </c>
       <c r="AC4" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="str">
+        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
+      </c>
       <c r="B5" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
-      <c r="C5" t="str">
-        <v>67592003</v>
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
       <c r="D5">
-        <v>12677050659</v>
+        <v>108024405000</v>
       </c>
       <c r="E5" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="G5" t="str">
+        <v>2026-07-29T00:00:00Z</v>
+      </c>
+      <c r="K5" t="str">
         <v>K34</v>
       </c>
-      <c r="F5" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="H5">
-        <v>10160960000</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="K5" t="str">
+      <c r="L5" t="str">
+        <v>Bulungan (Kab.)</v>
+      </c>
+      <c r="N5" t="str">
+        <v>2026-09-17T00:00:00Z</v>
+      </c>
+      <c r="R5" t="str">
+        <v>Kalimantan Utara</v>
+      </c>
+      <c r="S5">
+        <v>94577629145</v>
+      </c>
+      <c r="U5">
+        <v>10150225000</v>
+      </c>
+      <c r="V5" t="str">
+        <v>66390319</v>
+      </c>
+      <c r="X5">
+        <v>2026</v>
+      </c>
+      <c r="Y5">
+        <v>194</v>
+      </c>
+      <c r="Z5" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M5">
-        <v>10153666000</v>
-      </c>
-      <c r="N5" t="str">
-        <v>2026-10-07T00:00:00Z</v>
-      </c>
-      <c r="O5" t="str">
-        <v>Jl Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="P5">
-        <v>2026</v>
-      </c>
-      <c r="R5" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="T5" t="str">
-        <v>452677</v>
-      </c>
-      <c r="Y5">
-        <v>14699105000</v>
-      </c>
-      <c r="AA5">
-        <v>194</v>
-      </c>
-      <c r="AB5" t="str">
-        <v>KEMENTERIAN</v>
+      <c r="AA5" t="str">
+        <v>626131</v>
+      </c>
+      <c r="AB5">
+        <v>10157189000</v>
       </c>
       <c r="AC5" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="str">
+        <v>Jl. Jend Gatot Subroto Kav 51</v>
+      </c>
       <c r="B6" t="str">
-        <v>2026-08-20T00:00:00Z</v>
-      </c>
-      <c r="C6" t="str">
-        <v>67538462</v>
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
       <c r="D6">
-        <v>646650000</v>
+        <v>400000000</v>
       </c>
       <c r="E6" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="G6" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="K6" t="str">
         <v>K34</v>
       </c>
-      <c r="F6" t="str">
+      <c r="L6" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="N6" t="str">
+        <v>2026-09-18T00:00:00Z</v>
+      </c>
+      <c r="R6" t="str">
         <v>DKI Jakarta</v>
       </c>
-      <c r="H6">
-        <v>10162858000</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="K6" t="str">
+      <c r="S6">
+        <v>294600000</v>
+      </c>
+      <c r="U6">
+        <v>10152339000</v>
+      </c>
+      <c r="V6" t="str">
+        <v>67611590</v>
+      </c>
+      <c r="X6">
+        <v>2026</v>
+      </c>
+      <c r="Y6">
+        <v>194</v>
+      </c>
+      <c r="Z6" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M6">
-        <v>10155417000</v>
-      </c>
-      <c r="N6" t="str">
-        <v>2026-09-23T00:00:00Z</v>
-      </c>
-      <c r="O6" t="str">
-        <v>Jl Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="P6">
-        <v>2026</v>
-      </c>
-      <c r="R6" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="T6" t="str">
+      <c r="AA6" t="str">
         <v>452677</v>
       </c>
-      <c r="Y6">
-        <v>654750000</v>
-      </c>
-      <c r="AA6">
-        <v>194</v>
-      </c>
-      <c r="AB6" t="str">
-        <v>KEMENTERIAN</v>
+      <c r="AB6">
+        <v>10159515000</v>
       </c>
       <c r="AC6" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="str">
+        <v>Jl Jend Gatot Subroto Kav 51</v>
+      </c>
       <c r="B7" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="C7" t="str">
-        <v>66390318</v>
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
       <c r="D7">
-        <v>72210016000</v>
+        <v>14699105000</v>
       </c>
       <c r="E7" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="G7" t="str">
+        <v>2026-08-21T00:00:00Z</v>
+      </c>
+      <c r="K7" t="str">
         <v>K34</v>
       </c>
-      <c r="F7" t="str">
-        <v>Maluku Utara</v>
-      </c>
-      <c r="H7">
-        <v>10158222000</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Halmahera Selatan (Kab.)</v>
-      </c>
-      <c r="K7" t="str">
+      <c r="L7" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="N7" t="str">
+        <v>2026-10-07T00:00:00Z</v>
+      </c>
+      <c r="R7" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="S7">
+        <v>12677050659</v>
+      </c>
+      <c r="U7">
+        <v>10153666000</v>
+      </c>
+      <c r="V7" t="str">
+        <v>67592003</v>
+      </c>
+      <c r="X7">
+        <v>2026</v>
+      </c>
+      <c r="Y7">
+        <v>194</v>
+      </c>
+      <c r="Z7" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M7">
-        <v>10151157000</v>
-      </c>
-      <c r="N7" t="str">
-        <v>2026-09-16T00:00:00Z</v>
-      </c>
-      <c r="O7" t="str">
-        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
-      </c>
-      <c r="P7">
-        <v>2026</v>
-      </c>
-      <c r="R7" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="T7" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Y7">
-        <v>72311690000</v>
-      </c>
-      <c r="AA7">
-        <v>194</v>
-      </c>
-      <c r="AB7" t="str">
-        <v>KEMENTERIAN</v>
+      <c r="AA7" t="str">
+        <v>452677</v>
+      </c>
+      <c r="AB7">
+        <v>10160960000</v>
       </c>
       <c r="AC7" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
       </c>
     </row>
     <row r="8">
+      <c r="A8" t="str">
+        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
+      </c>
       <c r="B8" t="str">
-        <v>2026-07-22T00:00:00Z</v>
-      </c>
-      <c r="C8" t="str">
-        <v>67429813</v>
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
       <c r="D8">
-        <v>2299921875</v>
+        <v>72311690000</v>
       </c>
       <c r="E8" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="G8" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="K8" t="str">
         <v>K34</v>
       </c>
-      <c r="F8" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="H8">
-        <v>10151353000</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="K8" t="str">
+      <c r="L8" t="str">
+        <v>Halmahera Selatan (Kab.)</v>
+      </c>
+      <c r="N8" t="str">
+        <v>2026-09-16T00:00:00Z</v>
+      </c>
+      <c r="R8" t="str">
+        <v>Maluku Utara</v>
+      </c>
+      <c r="S8">
+        <v>72210016000</v>
+      </c>
+      <c r="U8">
+        <v>10151157000</v>
+      </c>
+      <c r="V8" t="str">
+        <v>66390318</v>
+      </c>
+      <c r="X8">
+        <v>2026</v>
+      </c>
+      <c r="Y8">
+        <v>194</v>
+      </c>
+      <c r="Z8" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="M8">
-        <v>10144772000</v>
-      </c>
-      <c r="N8" t="str">
-        <v>2026-08-26T00:00:00Z</v>
-      </c>
-      <c r="O8" t="str">
-        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
-      </c>
-      <c r="P8">
-        <v>2026</v>
-      </c>
-      <c r="R8" t="str">
-        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
-      </c>
-      <c r="T8" t="str">
-        <v>626132</v>
-      </c>
-      <c r="Y8">
-        <v>2300000000</v>
-      </c>
-      <c r="AA8">
-        <v>194</v>
-      </c>
-      <c r="AB8" t="str">
-        <v>KEMENTERIAN</v>
+      <c r="AA8" t="str">
+        <v>626131</v>
+      </c>
+      <c r="AB8">
+        <v>10158222000</v>
       </c>
       <c r="AC8" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cfGQhqjeisnhEK0l.olftb-mSmY5rQCNxtVl09-PYPC4Of48sJfJcus4O92w</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
+++ b/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
@@ -397,92 +397,92 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>tgl_penetapan_pemenang</v>
+      </c>
+      <c r="B1" t="str">
+        <v>kabkota</v>
+      </c>
+      <c r="C1" t="str">
+        <v>kd_satker</v>
+      </c>
+      <c r="D1" t="str">
+        <v>nilai_negosiasi</v>
+      </c>
+      <c r="E1" t="str">
+        <v>nilai_umk_kontrak</v>
+      </c>
+      <c r="F1" t="str">
+        <v>tahun_anggaran</v>
+      </c>
+      <c r="G1" t="str">
+        <v>nilai_pdn_kontrak</v>
+      </c>
+      <c r="H1" t="str">
+        <v>jenis_klpd</v>
+      </c>
+      <c r="I1" t="str">
         <v>lokasi_pekerjaan</v>
       </c>
-      <c r="B1" t="str">
-        <v>nama_satker</v>
-      </c>
-      <c r="C1" t="str">
-        <v>npwp_penyedia</v>
-      </c>
-      <c r="D1" t="str">
-        <v>pagu</v>
-      </c>
-      <c r="E1" t="str">
-        <v>jenis_klpd</v>
-      </c>
-      <c r="F1" t="str">
-        <v>nilai_terkoreksi</v>
-      </c>
-      <c r="G1" t="str">
-        <v>tgl_pengumuman_tender</v>
-      </c>
-      <c r="H1" t="str">
+      <c r="J1" t="str">
         <v>kd_penyedia</v>
       </c>
-      <c r="I1" t="str">
+      <c r="K1" t="str">
+        <v>nilai_kontrak</v>
+      </c>
+      <c r="L1" t="str">
+        <v>kd_rup_paket</v>
+      </c>
+      <c r="M1" t="str">
+        <v>kd_tender</v>
+      </c>
+      <c r="N1" t="str">
         <v>nama_penyedia</v>
       </c>
-      <c r="J1" t="str">
-        <v>nilai_pdn_kontrak</v>
-      </c>
-      <c r="K1" t="str">
+      <c r="O1" t="str">
         <v>kd_klpd</v>
       </c>
-      <c r="L1" t="str">
-        <v>kabkota</v>
-      </c>
-      <c r="M1" t="str">
-        <v>nilai_negosiasi</v>
-      </c>
-      <c r="N1" t="str">
-        <v>tgl_penetapan_pemenang</v>
-      </c>
-      <c r="O1" t="str">
-        <v>nilai_penawaran</v>
-      </c>
       <c r="P1" t="str">
-        <v>nilai_umk_kontrak</v>
+        <v>provinsi</v>
       </c>
       <c r="Q1" t="str">
         <v>psr_id</v>
       </c>
       <c r="R1" t="str">
-        <v>provinsi</v>
+        <v>tgl_pengumuman_tender</v>
       </c>
       <c r="S1" t="str">
+        <v>npwp_penyedia</v>
+      </c>
+      <c r="T1" t="str">
+        <v>kd_paket</v>
+      </c>
+      <c r="U1" t="str">
+        <v>nilai_terkoreksi</v>
+      </c>
+      <c r="V1" t="str">
+        <v>pagu</v>
+      </c>
+      <c r="W1" t="str">
+        <v>nama_satker</v>
+      </c>
+      <c r="X1" t="str">
         <v>hps</v>
       </c>
-      <c r="T1" t="str">
-        <v>nilai_kontrak</v>
-      </c>
-      <c r="U1" t="str">
-        <v>kd_paket</v>
-      </c>
-      <c r="V1" t="str">
-        <v>kd_rup_paket</v>
-      </c>
-      <c r="W1" t="str">
+      <c r="Y1" t="str">
         <v>npwp_16_penyedia</v>
       </c>
-      <c r="X1" t="str">
-        <v>tahun_anggaran</v>
-      </c>
-      <c r="Y1" t="str">
+      <c r="Z1" t="str">
         <v>kd_lpse</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AA1" t="str">
         <v>nama_klpd</v>
       </c>
-      <c r="AA1" t="str">
-        <v>kd_satker</v>
-      </c>
       <c r="AB1" t="str">
-        <v>kd_tender</v>
+        <v>nilai_penawaran</v>
       </c>
       <c r="AC1" t="str">
         <v>last_update_ref</v>
@@ -490,426 +490,482 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>2026-10-01T00:00:00Z</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Bengkulu (Kota)</v>
+      </c>
+      <c r="C2" t="str">
+        <v>626131</v>
+      </c>
+      <c r="F2">
+        <v>2026</v>
+      </c>
+      <c r="H2" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I2" t="str">
         <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
       </c>
-      <c r="B2" t="str">
+      <c r="L2" t="str">
+        <v>66390312</v>
+      </c>
+      <c r="M2">
+        <v>10159959000</v>
+      </c>
+      <c r="O2" t="str">
+        <v>K34</v>
+      </c>
+      <c r="P2" t="str">
+        <v>Bengkulu</v>
+      </c>
+      <c r="R2" t="str">
+        <v>2026-08-21T00:00:00Z</v>
+      </c>
+      <c r="T2">
+        <v>10152741000</v>
+      </c>
+      <c r="V2">
+        <v>63441052000</v>
+      </c>
+      <c r="W2" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="D2">
-        <v>63441052000</v>
-      </c>
-      <c r="E2" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="G2" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
-      <c r="K2" t="str">
-        <v>K34</v>
-      </c>
-      <c r="L2" t="str">
-        <v>Bengkulu (Kota)</v>
-      </c>
-      <c r="N2" t="str">
-        <v>2026-10-01T00:00:00Z</v>
-      </c>
-      <c r="R2" t="str">
-        <v>Bengkulu</v>
-      </c>
-      <c r="S2">
+      <c r="X2">
         <v>51439625000</v>
       </c>
-      <c r="U2">
-        <v>10152741000</v>
-      </c>
-      <c r="V2" t="str">
-        <v>66390312</v>
-      </c>
-      <c r="X2">
-        <v>2026</v>
-      </c>
-      <c r="Y2">
+      <c r="Z2">
         <v>194</v>
       </c>
-      <c r="Z2" t="str">
+      <c r="AA2" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="AA2" t="str">
-        <v>626131</v>
-      </c>
-      <c r="AB2">
-        <v>10159959000</v>
-      </c>
       <c r="AC2" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
+        <v>2026-10-06T00:00:00Z</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Batam (Kota)</v>
+      </c>
+      <c r="C3" t="str">
+        <v>626131</v>
+      </c>
+      <c r="F3">
+        <v>2026</v>
+      </c>
+      <c r="H3" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I3" t="str">
         <v>Desa Batu Besar, Kecamatan Nongsa, Kota Batam, Provinsi Kepulauan Riau</v>
       </c>
-      <c r="B3" t="str">
+      <c r="L3" t="str">
+        <v>66390327</v>
+      </c>
+      <c r="M3">
+        <v>10163085000</v>
+      </c>
+      <c r="O3" t="str">
+        <v>K34</v>
+      </c>
+      <c r="P3" t="str">
+        <v>Kepulauan Riau</v>
+      </c>
+      <c r="R3" t="str">
+        <v>2026-08-28T00:00:00Z</v>
+      </c>
+      <c r="T3">
+        <v>10155602000</v>
+      </c>
+      <c r="V3">
+        <v>54624000000</v>
+      </c>
+      <c r="W3" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="D3">
-        <v>54624000000</v>
-      </c>
-      <c r="E3" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="G3" t="str">
-        <v>2026-08-28T00:00:00Z</v>
-      </c>
-      <c r="K3" t="str">
-        <v>K34</v>
-      </c>
-      <c r="L3" t="str">
-        <v>Batam (Kota)</v>
-      </c>
-      <c r="N3" t="str">
-        <v>2026-10-06T00:00:00Z</v>
-      </c>
-      <c r="R3" t="str">
-        <v>Kepulauan Riau</v>
-      </c>
-      <c r="S3">
+      <c r="X3">
         <v>54472055602.06</v>
       </c>
-      <c r="U3">
-        <v>10155602000</v>
-      </c>
-      <c r="V3" t="str">
-        <v>66390327</v>
-      </c>
-      <c r="X3">
-        <v>2026</v>
-      </c>
-      <c r="Y3">
+      <c r="Z3">
         <v>194</v>
       </c>
-      <c r="Z3" t="str">
+      <c r="AA3" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="AA3" t="str">
-        <v>626131</v>
-      </c>
-      <c r="AB3">
-        <v>10163085000</v>
-      </c>
       <c r="AC3" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
+        <v>2026-08-27T00:00:00Z</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="C4" t="str">
+        <v>626132</v>
+      </c>
+      <c r="D4">
+        <v>2089050250</v>
+      </c>
+      <c r="F4">
+        <v>2026</v>
+      </c>
+      <c r="H4" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I4" t="str">
         <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
       </c>
-      <c r="B4" t="str">
-        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
-      </c>
-      <c r="C4" t="str">
-        <v>01.308.279.7-001.000</v>
-      </c>
-      <c r="D4">
-        <v>2300000000</v>
-      </c>
-      <c r="E4" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="F4">
+      <c r="J4">
+        <v>712065</v>
+      </c>
+      <c r="K4">
         <v>2089050250</v>
       </c>
-      <c r="G4" t="str">
-        <v>2026-07-22T00:00:00Z</v>
-      </c>
-      <c r="H4">
-        <v>712065</v>
-      </c>
-      <c r="I4" t="str">
+      <c r="L4" t="str">
+        <v>67429813</v>
+      </c>
+      <c r="M4">
+        <v>10151353000</v>
+      </c>
+      <c r="N4" t="str">
         <v>PT INERSIA AMPAK ENGINEERS</v>
       </c>
-      <c r="K4" t="str">
+      <c r="O4" t="str">
         <v>K34</v>
       </c>
-      <c r="L4" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="M4">
-        <v>2089050250</v>
-      </c>
-      <c r="N4" t="str">
-        <v>2026-08-27T00:00:00Z</v>
-      </c>
-      <c r="O4">
-        <v>2089050250</v>
+      <c r="P4" t="str">
+        <v>DKI Jakarta</v>
       </c>
       <c r="Q4">
         <v>11760143000</v>
       </c>
       <c r="R4" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="S4">
+        <v>2026-07-22T00:00:00Z</v>
+      </c>
+      <c r="S4" t="str">
+        <v>01.308.279.7-001.000</v>
+      </c>
+      <c r="T4">
+        <v>10144772000</v>
+      </c>
+      <c r="U4">
+        <v>2089050250</v>
+      </c>
+      <c r="V4">
+        <v>2300000000</v>
+      </c>
+      <c r="W4" t="str">
+        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
+      </c>
+      <c r="X4">
         <v>2299921875</v>
       </c>
-      <c r="T4">
+      <c r="Y4" t="str">
+        <v>0013082797001000</v>
+      </c>
+      <c r="Z4">
+        <v>194</v>
+      </c>
+      <c r="AA4" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="AB4">
         <v>2089050250</v>
       </c>
-      <c r="U4">
-        <v>10144772000</v>
-      </c>
-      <c r="V4" t="str">
-        <v>67429813</v>
-      </c>
-      <c r="W4" t="str">
-        <v>0013082797001000</v>
-      </c>
-      <c r="X4">
-        <v>2026</v>
-      </c>
-      <c r="Y4">
-        <v>194</v>
-      </c>
-      <c r="Z4" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="AA4" t="str">
-        <v>626132</v>
-      </c>
-      <c r="AB4">
-        <v>10151353000</v>
-      </c>
       <c r="AC4" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
+        <v>2026-09-17T00:00:00Z</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Bulungan (Kab.)</v>
+      </c>
+      <c r="C5" t="str">
+        <v>626131</v>
+      </c>
+      <c r="F5">
+        <v>2026</v>
+      </c>
+      <c r="H5" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I5" t="str">
         <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
       </c>
-      <c r="B5" t="str">
+      <c r="L5" t="str">
+        <v>66390319</v>
+      </c>
+      <c r="M5">
+        <v>10157189000</v>
+      </c>
+      <c r="O5" t="str">
+        <v>K34</v>
+      </c>
+      <c r="P5" t="str">
+        <v>Kalimantan Utara</v>
+      </c>
+      <c r="R5" t="str">
+        <v>2026-07-29T00:00:00Z</v>
+      </c>
+      <c r="T5">
+        <v>10150225000</v>
+      </c>
+      <c r="V5">
+        <v>108024405000</v>
+      </c>
+      <c r="W5" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="D5">
-        <v>108024405000</v>
-      </c>
-      <c r="E5" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="G5" t="str">
-        <v>2026-07-29T00:00:00Z</v>
-      </c>
-      <c r="K5" t="str">
-        <v>K34</v>
-      </c>
-      <c r="L5" t="str">
-        <v>Bulungan (Kab.)</v>
-      </c>
-      <c r="N5" t="str">
-        <v>2026-09-17T00:00:00Z</v>
-      </c>
-      <c r="R5" t="str">
-        <v>Kalimantan Utara</v>
-      </c>
-      <c r="S5">
+      <c r="X5">
         <v>94577629145</v>
       </c>
-      <c r="U5">
-        <v>10150225000</v>
-      </c>
-      <c r="V5" t="str">
-        <v>66390319</v>
-      </c>
-      <c r="X5">
-        <v>2026</v>
-      </c>
-      <c r="Y5">
+      <c r="Z5">
         <v>194</v>
       </c>
-      <c r="Z5" t="str">
+      <c r="AA5" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="AA5" t="str">
-        <v>626131</v>
-      </c>
-      <c r="AB5">
-        <v>10157189000</v>
-      </c>
       <c r="AC5" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>2026-09-18T00:00:00Z</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>452677</v>
+      </c>
+      <c r="F6">
+        <v>2026</v>
+      </c>
+      <c r="H6" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I6" t="str">
         <v>Jl. Jend Gatot Subroto Kav 51</v>
       </c>
-      <c r="B6" t="str">
+      <c r="L6" t="str">
+        <v>67611590</v>
+      </c>
+      <c r="M6">
+        <v>10159515000</v>
+      </c>
+      <c r="O6" t="str">
+        <v>K34</v>
+      </c>
+      <c r="P6" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="R6" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="T6">
+        <v>10152339000</v>
+      </c>
+      <c r="V6">
+        <v>400000000</v>
+      </c>
+      <c r="W6" t="str">
         <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
-      <c r="D6">
-        <v>400000000</v>
-      </c>
-      <c r="E6" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="G6" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="K6" t="str">
-        <v>K34</v>
-      </c>
-      <c r="L6" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="N6" t="str">
-        <v>2026-09-18T00:00:00Z</v>
-      </c>
-      <c r="R6" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="S6">
+      <c r="X6">
         <v>294600000</v>
       </c>
-      <c r="U6">
-        <v>10152339000</v>
-      </c>
-      <c r="V6" t="str">
-        <v>67611590</v>
-      </c>
-      <c r="X6">
-        <v>2026</v>
-      </c>
-      <c r="Y6">
+      <c r="Z6">
         <v>194</v>
       </c>
-      <c r="Z6" t="str">
+      <c r="AA6" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="AA6" t="str">
-        <v>452677</v>
-      </c>
-      <c r="AB6">
-        <v>10159515000</v>
-      </c>
       <c r="AC6" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
+        <v>2026-10-07T00:00:00Z</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="C7" t="str">
+        <v>452677</v>
+      </c>
+      <c r="F7">
+        <v>2026</v>
+      </c>
+      <c r="H7" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I7" t="str">
         <v>Jl Jend Gatot Subroto Kav 51</v>
       </c>
-      <c r="B7" t="str">
+      <c r="L7" t="str">
+        <v>67592003</v>
+      </c>
+      <c r="M7">
+        <v>10160960000</v>
+      </c>
+      <c r="O7" t="str">
+        <v>K34</v>
+      </c>
+      <c r="P7" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="R7" t="str">
+        <v>2026-08-21T00:00:00Z</v>
+      </c>
+      <c r="T7">
+        <v>10153666000</v>
+      </c>
+      <c r="V7">
+        <v>14699105000</v>
+      </c>
+      <c r="W7" t="str">
         <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
-      <c r="D7">
-        <v>14699105000</v>
-      </c>
-      <c r="E7" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="G7" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
-      <c r="K7" t="str">
-        <v>K34</v>
-      </c>
-      <c r="L7" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="N7" t="str">
-        <v>2026-10-07T00:00:00Z</v>
-      </c>
-      <c r="R7" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="S7">
+      <c r="X7">
         <v>12677050659</v>
       </c>
-      <c r="U7">
-        <v>10153666000</v>
-      </c>
-      <c r="V7" t="str">
-        <v>67592003</v>
-      </c>
-      <c r="X7">
-        <v>2026</v>
-      </c>
-      <c r="Y7">
+      <c r="Z7">
         <v>194</v>
       </c>
-      <c r="Z7" t="str">
+      <c r="AA7" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="AA7" t="str">
-        <v>452677</v>
-      </c>
-      <c r="AB7">
-        <v>10160960000</v>
-      </c>
       <c r="AC7" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
+        <v>2026-09-23T00:00:00Z</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="C8" t="str">
+        <v>452677</v>
+      </c>
+      <c r="F8">
+        <v>2026</v>
+      </c>
+      <c r="H8" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Jl Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="L8" t="str">
+        <v>67538462</v>
+      </c>
+      <c r="M8">
+        <v>10162858000</v>
+      </c>
+      <c r="O8" t="str">
+        <v>K34</v>
+      </c>
+      <c r="P8" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="R8" t="str">
+        <v>2026-08-20T00:00:00Z</v>
+      </c>
+      <c r="T8">
+        <v>10155417000</v>
+      </c>
+      <c r="V8">
+        <v>654750000</v>
+      </c>
+      <c r="W8" t="str">
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      </c>
+      <c r="X8">
+        <v>646650000</v>
+      </c>
+      <c r="Z8">
+        <v>194</v>
+      </c>
+      <c r="AA8" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="AC8" t="str">
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>2026-09-16T00:00:00Z</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Halmahera Selatan (Kab.)</v>
+      </c>
+      <c r="C9" t="str">
+        <v>626131</v>
+      </c>
+      <c r="F9">
+        <v>2026</v>
+      </c>
+      <c r="H9" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I9" t="str">
         <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
       </c>
-      <c r="B8" t="str">
+      <c r="L9" t="str">
+        <v>66390318</v>
+      </c>
+      <c r="M9">
+        <v>10158222000</v>
+      </c>
+      <c r="O9" t="str">
+        <v>K34</v>
+      </c>
+      <c r="P9" t="str">
+        <v>Maluku Utara</v>
+      </c>
+      <c r="R9" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="T9">
+        <v>10151157000</v>
+      </c>
+      <c r="V9">
+        <v>72311690000</v>
+      </c>
+      <c r="W9" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="D8">
-        <v>72311690000</v>
-      </c>
-      <c r="E8" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="G8" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="K8" t="str">
-        <v>K34</v>
-      </c>
-      <c r="L8" t="str">
-        <v>Halmahera Selatan (Kab.)</v>
-      </c>
-      <c r="N8" t="str">
-        <v>2026-09-16T00:00:00Z</v>
-      </c>
-      <c r="R8" t="str">
-        <v>Maluku Utara</v>
-      </c>
-      <c r="S8">
+      <c r="X9">
         <v>72210016000</v>
       </c>
-      <c r="U8">
-        <v>10151157000</v>
-      </c>
-      <c r="V8" t="str">
-        <v>66390318</v>
-      </c>
-      <c r="X8">
-        <v>2026</v>
-      </c>
-      <c r="Y8">
+      <c r="Z9">
         <v>194</v>
       </c>
-      <c r="Z8" t="str">
+      <c r="AA9" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="AA8" t="str">
-        <v>626131</v>
-      </c>
-      <c r="AB8">
-        <v>10158222000</v>
-      </c>
-      <c r="AC8" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.axvfa4oWVgswa3t1.IwhzhPkIX-8t_PXzVgCy_81fkyJcabzSINpeeCnXJAA</v>
+      <c r="AC9" t="str">
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
+++ b/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
@@ -404,82 +404,82 @@
         <v>tgl_penetapan_pemenang</v>
       </c>
       <c r="B1" t="str">
+        <v>npwp_16_penyedia</v>
+      </c>
+      <c r="C1" t="str">
+        <v>nilai_umk_kontrak</v>
+      </c>
+      <c r="D1" t="str">
+        <v>kd_penyedia</v>
+      </c>
+      <c r="E1" t="str">
+        <v>kd_satker</v>
+      </c>
+      <c r="F1" t="str">
+        <v>pagu</v>
+      </c>
+      <c r="G1" t="str">
+        <v>nilai_kontrak</v>
+      </c>
+      <c r="H1" t="str">
+        <v>tgl_pengumuman_tender</v>
+      </c>
+      <c r="I1" t="str">
+        <v>nilai_terkoreksi</v>
+      </c>
+      <c r="J1" t="str">
+        <v>kd_tender</v>
+      </c>
+      <c r="K1" t="str">
+        <v>psr_id</v>
+      </c>
+      <c r="L1" t="str">
+        <v>kd_klpd</v>
+      </c>
+      <c r="M1" t="str">
+        <v>npwp_penyedia</v>
+      </c>
+      <c r="N1" t="str">
         <v>kabkota</v>
       </c>
-      <c r="C1" t="str">
-        <v>kd_satker</v>
-      </c>
-      <c r="D1" t="str">
+      <c r="O1" t="str">
+        <v>nilai_pdn_kontrak</v>
+      </c>
+      <c r="P1" t="str">
+        <v>nama_satker</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>hps</v>
+      </c>
+      <c r="R1" t="str">
+        <v>kd_lpse</v>
+      </c>
+      <c r="S1" t="str">
+        <v>kd_paket</v>
+      </c>
+      <c r="T1" t="str">
+        <v>tahun_anggaran</v>
+      </c>
+      <c r="U1" t="str">
+        <v>nama_klpd</v>
+      </c>
+      <c r="V1" t="str">
         <v>nilai_negosiasi</v>
       </c>
-      <c r="E1" t="str">
-        <v>nilai_umk_kontrak</v>
-      </c>
-      <c r="F1" t="str">
-        <v>tahun_anggaran</v>
-      </c>
-      <c r="G1" t="str">
-        <v>nilai_pdn_kontrak</v>
-      </c>
-      <c r="H1" t="str">
+      <c r="W1" t="str">
+        <v>provinsi</v>
+      </c>
+      <c r="X1" t="str">
         <v>jenis_klpd</v>
       </c>
-      <c r="I1" t="str">
+      <c r="Y1" t="str">
         <v>lokasi_pekerjaan</v>
       </c>
-      <c r="J1" t="str">
-        <v>kd_penyedia</v>
-      </c>
-      <c r="K1" t="str">
-        <v>nilai_kontrak</v>
-      </c>
-      <c r="L1" t="str">
+      <c r="Z1" t="str">
+        <v>nama_penyedia</v>
+      </c>
+      <c r="AA1" t="str">
         <v>kd_rup_paket</v>
-      </c>
-      <c r="M1" t="str">
-        <v>kd_tender</v>
-      </c>
-      <c r="N1" t="str">
-        <v>nama_penyedia</v>
-      </c>
-      <c r="O1" t="str">
-        <v>kd_klpd</v>
-      </c>
-      <c r="P1" t="str">
-        <v>provinsi</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>psr_id</v>
-      </c>
-      <c r="R1" t="str">
-        <v>tgl_pengumuman_tender</v>
-      </c>
-      <c r="S1" t="str">
-        <v>npwp_penyedia</v>
-      </c>
-      <c r="T1" t="str">
-        <v>kd_paket</v>
-      </c>
-      <c r="U1" t="str">
-        <v>nilai_terkoreksi</v>
-      </c>
-      <c r="V1" t="str">
-        <v>pagu</v>
-      </c>
-      <c r="W1" t="str">
-        <v>nama_satker</v>
-      </c>
-      <c r="X1" t="str">
-        <v>hps</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>npwp_16_penyedia</v>
-      </c>
-      <c r="Z1" t="str">
-        <v>kd_lpse</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>nama_klpd</v>
       </c>
       <c r="AB1" t="str">
         <v>nilai_penawaran</v>
@@ -492,112 +492,112 @@
       <c r="A2" t="str">
         <v>2026-10-01T00:00:00Z</v>
       </c>
-      <c r="B2" t="str">
+      <c r="E2" t="str">
+        <v>626131</v>
+      </c>
+      <c r="F2">
+        <v>63441052000</v>
+      </c>
+      <c r="H2" t="str">
+        <v>2026-08-21T00:00:00Z</v>
+      </c>
+      <c r="J2">
+        <v>10159959000</v>
+      </c>
+      <c r="L2" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N2" t="str">
         <v>Bengkulu (Kota)</v>
       </c>
-      <c r="C2" t="str">
-        <v>626131</v>
-      </c>
-      <c r="F2">
+      <c r="P2" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="Q2">
+        <v>51439625000</v>
+      </c>
+      <c r="R2">
+        <v>194</v>
+      </c>
+      <c r="S2">
+        <v>10152741000</v>
+      </c>
+      <c r="T2">
         <v>2026</v>
       </c>
-      <c r="H2" t="str">
+      <c r="U2" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="W2" t="str">
+        <v>Bengkulu</v>
+      </c>
+      <c r="X2" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="I2" t="str">
+      <c r="Y2" t="str">
         <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
       </c>
-      <c r="L2" t="str">
+      <c r="AA2" t="str">
         <v>66390312</v>
       </c>
-      <c r="M2">
-        <v>10159959000</v>
-      </c>
-      <c r="O2" t="str">
-        <v>K34</v>
-      </c>
-      <c r="P2" t="str">
-        <v>Bengkulu</v>
-      </c>
-      <c r="R2" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
-      <c r="T2">
-        <v>10152741000</v>
-      </c>
-      <c r="V2">
-        <v>63441052000</v>
-      </c>
-      <c r="W2" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="X2">
-        <v>51439625000</v>
-      </c>
-      <c r="Z2">
-        <v>194</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
       <c r="AC2" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.WMOtntm-LpNfotwl.qxShH1_FUn5hy27jFRXkYBRVhq2gdFbWN6YwP5Yl9Gg</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
         <v>2026-10-06T00:00:00Z</v>
       </c>
-      <c r="B3" t="str">
+      <c r="E3" t="str">
+        <v>626131</v>
+      </c>
+      <c r="F3">
+        <v>54624000000</v>
+      </c>
+      <c r="H3" t="str">
+        <v>2026-08-28T00:00:00Z</v>
+      </c>
+      <c r="J3">
+        <v>10163085000</v>
+      </c>
+      <c r="L3" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N3" t="str">
         <v>Batam (Kota)</v>
       </c>
-      <c r="C3" t="str">
-        <v>626131</v>
-      </c>
-      <c r="F3">
+      <c r="P3" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="Q3">
+        <v>54472055602.06</v>
+      </c>
+      <c r="R3">
+        <v>194</v>
+      </c>
+      <c r="S3">
+        <v>10155602000</v>
+      </c>
+      <c r="T3">
         <v>2026</v>
       </c>
-      <c r="H3" t="str">
+      <c r="U3" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="W3" t="str">
+        <v>Kepulauan Riau</v>
+      </c>
+      <c r="X3" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="I3" t="str">
+      <c r="Y3" t="str">
         <v>Desa Batu Besar, Kecamatan Nongsa, Kota Batam, Provinsi Kepulauan Riau</v>
       </c>
-      <c r="L3" t="str">
+      <c r="AA3" t="str">
         <v>66390327</v>
       </c>
-      <c r="M3">
-        <v>10163085000</v>
-      </c>
-      <c r="O3" t="str">
-        <v>K34</v>
-      </c>
-      <c r="P3" t="str">
-        <v>Kepulauan Riau</v>
-      </c>
-      <c r="R3" t="str">
-        <v>2026-08-28T00:00:00Z</v>
-      </c>
-      <c r="T3">
-        <v>10155602000</v>
-      </c>
-      <c r="V3">
-        <v>54624000000</v>
-      </c>
-      <c r="W3" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="X3">
-        <v>54472055602.06</v>
-      </c>
-      <c r="Z3">
-        <v>194</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
       <c r="AC3" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.WMOtntm-LpNfotwl.qxShH1_FUn5hy27jFRXkYBRVhq2gdFbWN6YwP5Yl9Gg</v>
       </c>
     </row>
     <row r="4">
@@ -605,362 +605,362 @@
         <v>2026-08-27T00:00:00Z</v>
       </c>
       <c r="B4" t="str">
+        <v>0013082797001000</v>
+      </c>
+      <c r="D4">
+        <v>712065</v>
+      </c>
+      <c r="E4" t="str">
+        <v>626132</v>
+      </c>
+      <c r="F4">
+        <v>2300000000</v>
+      </c>
+      <c r="G4">
+        <v>2089050250</v>
+      </c>
+      <c r="H4" t="str">
+        <v>2026-07-22T00:00:00Z</v>
+      </c>
+      <c r="I4">
+        <v>2089050250</v>
+      </c>
+      <c r="J4">
+        <v>10151353000</v>
+      </c>
+      <c r="K4">
+        <v>11760143000</v>
+      </c>
+      <c r="L4" t="str">
+        <v>K34</v>
+      </c>
+      <c r="M4" t="str">
+        <v>01.308.279.7-001.000</v>
+      </c>
+      <c r="N4" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="C4" t="str">
-        <v>626132</v>
-      </c>
-      <c r="D4">
+      <c r="P4" t="str">
+        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
+      </c>
+      <c r="Q4">
+        <v>2299921875</v>
+      </c>
+      <c r="R4">
+        <v>194</v>
+      </c>
+      <c r="S4">
+        <v>10144772000</v>
+      </c>
+      <c r="T4">
+        <v>2026</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="V4">
         <v>2089050250</v>
       </c>
-      <c r="F4">
-        <v>2026</v>
-      </c>
-      <c r="H4" t="str">
+      <c r="W4" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="X4" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="I4" t="str">
+      <c r="Y4" t="str">
         <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
       </c>
-      <c r="J4">
-        <v>712065</v>
-      </c>
-      <c r="K4">
-        <v>2089050250</v>
-      </c>
-      <c r="L4" t="str">
+      <c r="Z4" t="str">
+        <v>PT INERSIA AMPAK ENGINEERS</v>
+      </c>
+      <c r="AA4" t="str">
         <v>67429813</v>
-      </c>
-      <c r="M4">
-        <v>10151353000</v>
-      </c>
-      <c r="N4" t="str">
-        <v>PT INERSIA AMPAK ENGINEERS</v>
-      </c>
-      <c r="O4" t="str">
-        <v>K34</v>
-      </c>
-      <c r="P4" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="Q4">
-        <v>11760143000</v>
-      </c>
-      <c r="R4" t="str">
-        <v>2026-07-22T00:00:00Z</v>
-      </c>
-      <c r="S4" t="str">
-        <v>01.308.279.7-001.000</v>
-      </c>
-      <c r="T4">
-        <v>10144772000</v>
-      </c>
-      <c r="U4">
-        <v>2089050250</v>
-      </c>
-      <c r="V4">
-        <v>2300000000</v>
-      </c>
-      <c r="W4" t="str">
-        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
-      </c>
-      <c r="X4">
-        <v>2299921875</v>
-      </c>
-      <c r="Y4" t="str">
-        <v>0013082797001000</v>
-      </c>
-      <c r="Z4">
-        <v>194</v>
-      </c>
-      <c r="AA4" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="AB4">
         <v>2089050250</v>
       </c>
       <c r="AC4" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.WMOtntm-LpNfotwl.qxShH1_FUn5hy27jFRXkYBRVhq2gdFbWN6YwP5Yl9Gg</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
         <v>2026-09-17T00:00:00Z</v>
       </c>
-      <c r="B5" t="str">
+      <c r="E5" t="str">
+        <v>626131</v>
+      </c>
+      <c r="F5">
+        <v>108024405000</v>
+      </c>
+      <c r="H5" t="str">
+        <v>2026-07-29T00:00:00Z</v>
+      </c>
+      <c r="J5">
+        <v>10157189000</v>
+      </c>
+      <c r="L5" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N5" t="str">
         <v>Bulungan (Kab.)</v>
       </c>
-      <c r="C5" t="str">
-        <v>626131</v>
-      </c>
-      <c r="F5">
+      <c r="P5" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="Q5">
+        <v>94577629145</v>
+      </c>
+      <c r="R5">
+        <v>194</v>
+      </c>
+      <c r="S5">
+        <v>10150225000</v>
+      </c>
+      <c r="T5">
         <v>2026</v>
       </c>
-      <c r="H5" t="str">
+      <c r="U5" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="W5" t="str">
+        <v>Kalimantan Utara</v>
+      </c>
+      <c r="X5" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="I5" t="str">
+      <c r="Y5" t="str">
         <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
       </c>
-      <c r="L5" t="str">
+      <c r="AA5" t="str">
         <v>66390319</v>
       </c>
-      <c r="M5">
-        <v>10157189000</v>
-      </c>
-      <c r="O5" t="str">
-        <v>K34</v>
-      </c>
-      <c r="P5" t="str">
-        <v>Kalimantan Utara</v>
-      </c>
-      <c r="R5" t="str">
-        <v>2026-07-29T00:00:00Z</v>
-      </c>
-      <c r="T5">
-        <v>10150225000</v>
-      </c>
-      <c r="V5">
-        <v>108024405000</v>
-      </c>
-      <c r="W5" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="X5">
-        <v>94577629145</v>
-      </c>
-      <c r="Z5">
-        <v>194</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
       <c r="AC5" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.WMOtntm-LpNfotwl.qxShH1_FUn5hy27jFRXkYBRVhq2gdFbWN6YwP5Yl9Gg</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
         <v>2026-09-18T00:00:00Z</v>
       </c>
-      <c r="B6" t="str">
+      <c r="E6" t="str">
+        <v>452677</v>
+      </c>
+      <c r="F6">
+        <v>400000000</v>
+      </c>
+      <c r="H6" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="J6">
+        <v>10159515000</v>
+      </c>
+      <c r="L6" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N6" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="C6" t="str">
-        <v>452677</v>
-      </c>
-      <c r="F6">
+      <c r="P6" t="str">
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      </c>
+      <c r="Q6">
+        <v>294600000</v>
+      </c>
+      <c r="R6">
+        <v>194</v>
+      </c>
+      <c r="S6">
+        <v>10152339000</v>
+      </c>
+      <c r="T6">
         <v>2026</v>
       </c>
-      <c r="H6" t="str">
+      <c r="U6" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="W6" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="X6" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="I6" t="str">
+      <c r="Y6" t="str">
         <v>Jl. Jend Gatot Subroto Kav 51</v>
       </c>
-      <c r="L6" t="str">
+      <c r="AA6" t="str">
         <v>67611590</v>
       </c>
-      <c r="M6">
-        <v>10159515000</v>
-      </c>
-      <c r="O6" t="str">
-        <v>K34</v>
-      </c>
-      <c r="P6" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="R6" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="T6">
-        <v>10152339000</v>
-      </c>
-      <c r="V6">
-        <v>400000000</v>
-      </c>
-      <c r="W6" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="X6">
-        <v>294600000</v>
-      </c>
-      <c r="Z6">
-        <v>194</v>
-      </c>
-      <c r="AA6" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
       <c r="AC6" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.WMOtntm-LpNfotwl.qxShH1_FUn5hy27jFRXkYBRVhq2gdFbWN6YwP5Yl9Gg</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
         <v>2026-10-07T00:00:00Z</v>
       </c>
-      <c r="B7" t="str">
+      <c r="E7" t="str">
+        <v>452677</v>
+      </c>
+      <c r="F7">
+        <v>14699105000</v>
+      </c>
+      <c r="H7" t="str">
+        <v>2026-08-21T00:00:00Z</v>
+      </c>
+      <c r="J7">
+        <v>10160960000</v>
+      </c>
+      <c r="L7" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N7" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="C7" t="str">
-        <v>452677</v>
-      </c>
-      <c r="F7">
+      <c r="P7" t="str">
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      </c>
+      <c r="Q7">
+        <v>12677050659</v>
+      </c>
+      <c r="R7">
+        <v>194</v>
+      </c>
+      <c r="S7">
+        <v>10153666000</v>
+      </c>
+      <c r="T7">
         <v>2026</v>
       </c>
-      <c r="H7" t="str">
+      <c r="U7" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="W7" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="X7" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="I7" t="str">
+      <c r="Y7" t="str">
         <v>Jl Jend Gatot Subroto Kav 51</v>
       </c>
-      <c r="L7" t="str">
+      <c r="AA7" t="str">
         <v>67592003</v>
       </c>
-      <c r="M7">
-        <v>10160960000</v>
-      </c>
-      <c r="O7" t="str">
-        <v>K34</v>
-      </c>
-      <c r="P7" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="R7" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
-      <c r="T7">
-        <v>10153666000</v>
-      </c>
-      <c r="V7">
-        <v>14699105000</v>
-      </c>
-      <c r="W7" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="X7">
-        <v>12677050659</v>
-      </c>
-      <c r="Z7">
-        <v>194</v>
-      </c>
-      <c r="AA7" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
       <c r="AC7" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.WMOtntm-LpNfotwl.qxShH1_FUn5hy27jFRXkYBRVhq2gdFbWN6YwP5Yl9Gg</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
         <v>2026-09-23T00:00:00Z</v>
       </c>
-      <c r="B8" t="str">
+      <c r="E8" t="str">
+        <v>452677</v>
+      </c>
+      <c r="F8">
+        <v>654750000</v>
+      </c>
+      <c r="H8" t="str">
+        <v>2026-08-20T00:00:00Z</v>
+      </c>
+      <c r="J8">
+        <v>10162858000</v>
+      </c>
+      <c r="L8" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N8" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="C8" t="str">
-        <v>452677</v>
-      </c>
-      <c r="F8">
+      <c r="P8" t="str">
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      </c>
+      <c r="Q8">
+        <v>646650000</v>
+      </c>
+      <c r="R8">
+        <v>194</v>
+      </c>
+      <c r="S8">
+        <v>10155417000</v>
+      </c>
+      <c r="T8">
         <v>2026</v>
       </c>
-      <c r="H8" t="str">
+      <c r="U8" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="W8" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="X8" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="I8" t="str">
+      <c r="Y8" t="str">
         <v>Jl Jend Gatot Subroto Kav 51</v>
       </c>
-      <c r="L8" t="str">
+      <c r="AA8" t="str">
         <v>67538462</v>
       </c>
-      <c r="M8">
-        <v>10162858000</v>
-      </c>
-      <c r="O8" t="str">
-        <v>K34</v>
-      </c>
-      <c r="P8" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="R8" t="str">
-        <v>2026-08-20T00:00:00Z</v>
-      </c>
-      <c r="T8">
-        <v>10155417000</v>
-      </c>
-      <c r="V8">
-        <v>654750000</v>
-      </c>
-      <c r="W8" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
-      </c>
-      <c r="X8">
-        <v>646650000</v>
-      </c>
-      <c r="Z8">
-        <v>194</v>
-      </c>
-      <c r="AA8" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
       <c r="AC8" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.WMOtntm-LpNfotwl.qxShH1_FUn5hy27jFRXkYBRVhq2gdFbWN6YwP5Yl9Gg</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
         <v>2026-09-16T00:00:00Z</v>
       </c>
-      <c r="B9" t="str">
+      <c r="E9" t="str">
+        <v>626131</v>
+      </c>
+      <c r="F9">
+        <v>72311690000</v>
+      </c>
+      <c r="H9" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="J9">
+        <v>10158222000</v>
+      </c>
+      <c r="L9" t="str">
+        <v>K34</v>
+      </c>
+      <c r="N9" t="str">
         <v>Halmahera Selatan (Kab.)</v>
       </c>
-      <c r="C9" t="str">
-        <v>626131</v>
-      </c>
-      <c r="F9">
+      <c r="P9" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="Q9">
+        <v>72210016000</v>
+      </c>
+      <c r="R9">
+        <v>194</v>
+      </c>
+      <c r="S9">
+        <v>10151157000</v>
+      </c>
+      <c r="T9">
         <v>2026</v>
       </c>
-      <c r="H9" t="str">
+      <c r="U9" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="W9" t="str">
+        <v>Maluku Utara</v>
+      </c>
+      <c r="X9" t="str">
         <v>KEMENTERIAN</v>
       </c>
-      <c r="I9" t="str">
+      <c r="Y9" t="str">
         <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
       </c>
-      <c r="L9" t="str">
+      <c r="AA9" t="str">
         <v>66390318</v>
       </c>
-      <c r="M9">
-        <v>10158222000</v>
-      </c>
-      <c r="O9" t="str">
-        <v>K34</v>
-      </c>
-      <c r="P9" t="str">
-        <v>Maluku Utara</v>
-      </c>
-      <c r="R9" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="T9">
-        <v>10151157000</v>
-      </c>
-      <c r="V9">
-        <v>72311690000</v>
-      </c>
-      <c r="W9" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
-      </c>
-      <c r="X9">
-        <v>72210016000</v>
-      </c>
-      <c r="Z9">
-        <v>194</v>
-      </c>
-      <c r="AA9" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
       <c r="AC9" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.tniNFPeHo4t2NfxS.AN16S4bnh1qoeprS0oRZ3wLmLy8Lmo7xM6sZgzOx93Q</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.WMOtntm-LpNfotwl.qxShH1_FUn5hy27jFRXkYBRVhq2gdFbWN6YwP5Yl9Gg</v>
       </c>
     </row>
   </sheetData>

--- a/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
+++ b/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
@@ -397,631 +397,687 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>kd_penyedia</v>
+      </c>
+      <c r="B1" t="str">
         <v>kd_rup_paket</v>
       </c>
-      <c r="B1" t="str">
+      <c r="C1" t="str">
+        <v>npwp_penyedia</v>
+      </c>
+      <c r="D1" t="str">
+        <v>tgl_penetapan_pemenang</v>
+      </c>
+      <c r="E1" t="str">
+        <v>nama_penyedia</v>
+      </c>
+      <c r="F1" t="str">
+        <v>kd_paket</v>
+      </c>
+      <c r="G1" t="str">
+        <v>jenis_klpd</v>
+      </c>
+      <c r="H1" t="str">
+        <v>psr_id</v>
+      </c>
+      <c r="I1" t="str">
+        <v>lokasi_pekerjaan</v>
+      </c>
+      <c r="J1" t="str">
+        <v>nama_satker</v>
+      </c>
+      <c r="K1" t="str">
         <v>npwp_16_penyedia</v>
       </c>
-      <c r="C1" t="str">
-        <v>nama_satker</v>
-      </c>
-      <c r="D1" t="str">
+      <c r="L1" t="str">
+        <v>hps</v>
+      </c>
+      <c r="M1" t="str">
+        <v>kd_lpse</v>
+      </c>
+      <c r="N1" t="str">
+        <v>nama_klpd</v>
+      </c>
+      <c r="O1" t="str">
         <v>kabkota</v>
       </c>
-      <c r="E1" t="str">
+      <c r="P1" t="str">
+        <v>kd_klpd</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>nilai_kontrak</v>
+      </c>
+      <c r="R1" t="str">
+        <v>nilai_pdn_kontrak</v>
+      </c>
+      <c r="S1" t="str">
+        <v>nilai_penawaran</v>
+      </c>
+      <c r="T1" t="str">
+        <v>kd_tender</v>
+      </c>
+      <c r="U1" t="str">
+        <v>provinsi</v>
+      </c>
+      <c r="V1" t="str">
+        <v>nilai_terkoreksi</v>
+      </c>
+      <c r="W1" t="str">
+        <v>pagu</v>
+      </c>
+      <c r="X1" t="str">
         <v>kd_satker</v>
       </c>
-      <c r="F1" t="str">
-        <v>nilai_kontrak</v>
-      </c>
-      <c r="G1" t="str">
-        <v>npwp_penyedia</v>
-      </c>
-      <c r="H1" t="str">
-        <v>lokasi_pekerjaan</v>
-      </c>
-      <c r="I1" t="str">
-        <v>nilai_umk_kontrak</v>
-      </c>
-      <c r="J1" t="str">
-        <v>provinsi</v>
-      </c>
-      <c r="K1" t="str">
-        <v>jenis_klpd</v>
-      </c>
-      <c r="L1" t="str">
-        <v>kd_paket</v>
-      </c>
-      <c r="M1" t="str">
+      <c r="Y1" t="str">
         <v>nilai_negosiasi</v>
-      </c>
-      <c r="N1" t="str">
-        <v>nilai_pdn_kontrak</v>
-      </c>
-      <c r="O1" t="str">
-        <v>nilai_penawaran</v>
-      </c>
-      <c r="P1" t="str">
-        <v>nilai_terkoreksi</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>tgl_pengumuman_tender</v>
-      </c>
-      <c r="R1" t="str">
-        <v>kd_penyedia</v>
-      </c>
-      <c r="S1" t="str">
-        <v>nama_klpd</v>
-      </c>
-      <c r="T1" t="str">
-        <v>tgl_penetapan_pemenang</v>
-      </c>
-      <c r="U1" t="str">
-        <v>psr_id</v>
-      </c>
-      <c r="V1" t="str">
-        <v>kd_klpd</v>
-      </c>
-      <c r="W1" t="str">
-        <v>nama_penyedia</v>
-      </c>
-      <c r="X1" t="str">
-        <v>hps</v>
-      </c>
-      <c r="Y1" t="str">
-        <v>kd_lpse</v>
       </c>
       <c r="Z1" t="str">
         <v>tahun_anggaran</v>
       </c>
       <c r="AA1" t="str">
-        <v>kd_tender</v>
+        <v>tgl_pengumuman_tender</v>
       </c>
       <c r="AB1" t="str">
-        <v>pagu</v>
+        <v>nilai_umk_kontrak</v>
       </c>
       <c r="AC1" t="str">
         <v>last_update_ref</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="str">
+      <c r="B2" t="str">
         <v>66390312</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
+        <v>2026-10-01T00:00:00Z</v>
+      </c>
+      <c r="F2">
+        <v>10152741000</v>
+      </c>
+      <c r="G2" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
+      </c>
+      <c r="J2" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="D2" t="str">
+      <c r="L2">
+        <v>51439625000</v>
+      </c>
+      <c r="M2">
+        <v>194</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="O2" t="str">
         <v>Bengkulu (Kota)</v>
       </c>
-      <c r="E2" t="str">
+      <c r="P2" t="str">
+        <v>K34</v>
+      </c>
+      <c r="T2">
+        <v>10159959000</v>
+      </c>
+      <c r="U2" t="str">
+        <v>Bengkulu</v>
+      </c>
+      <c r="W2">
+        <v>63441052000</v>
+      </c>
+      <c r="X2" t="str">
         <v>626131</v>
-      </c>
-      <c r="H2" t="str">
-        <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Bengkulu</v>
-      </c>
-      <c r="K2" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="L2">
-        <v>10152741000</v>
-      </c>
-      <c r="Q2" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
-      <c r="S2" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="T2" t="str">
-        <v>2026-10-01T00:00:00Z</v>
-      </c>
-      <c r="V2" t="str">
-        <v>K34</v>
-      </c>
-      <c r="X2">
-        <v>51439625000</v>
-      </c>
-      <c r="Y2">
-        <v>194</v>
       </c>
       <c r="Z2">
         <v>2026</v>
       </c>
-      <c r="AA2">
-        <v>10159959000</v>
-      </c>
-      <c r="AB2">
-        <v>63441052000</v>
+      <c r="AA2" t="str">
+        <v>2026-08-21T00:00:00Z</v>
       </c>
       <c r="AC2" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.iIBLUfZmUQ4kMoVj.Ckpn-Uob9HLP7YrWRTkTDbbfOIBHONTwrz8y1E4FjK0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
+      <c r="B3" t="str">
         <v>66390327</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
+        <v>2026-10-06T00:00:00Z</v>
+      </c>
+      <c r="F3">
+        <v>10155602000</v>
+      </c>
+      <c r="G3" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I3" t="str">
+        <v>Desa Batu Besar, Kecamatan Nongsa, Kota Batam, Provinsi Kepulauan Riau</v>
+      </c>
+      <c r="J3" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="D3" t="str">
+      <c r="L3">
+        <v>54472055602.06</v>
+      </c>
+      <c r="M3">
+        <v>194</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="O3" t="str">
         <v>Batam (Kota)</v>
       </c>
-      <c r="E3" t="str">
+      <c r="P3" t="str">
+        <v>K34</v>
+      </c>
+      <c r="T3">
+        <v>10163085000</v>
+      </c>
+      <c r="U3" t="str">
+        <v>Kepulauan Riau</v>
+      </c>
+      <c r="W3">
+        <v>54624000000</v>
+      </c>
+      <c r="X3" t="str">
         <v>626131</v>
-      </c>
-      <c r="H3" t="str">
-        <v>Desa Batu Besar, Kecamatan Nongsa, Kota Batam, Provinsi Kepulauan Riau</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Kepulauan Riau</v>
-      </c>
-      <c r="K3" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="L3">
-        <v>10155602000</v>
-      </c>
-      <c r="Q3" t="str">
-        <v>2026-08-28T00:00:00Z</v>
-      </c>
-      <c r="S3" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="T3" t="str">
-        <v>2026-10-06T00:00:00Z</v>
-      </c>
-      <c r="V3" t="str">
-        <v>K34</v>
-      </c>
-      <c r="X3">
-        <v>54472055602.06</v>
-      </c>
-      <c r="Y3">
-        <v>194</v>
       </c>
       <c r="Z3">
         <v>2026</v>
       </c>
-      <c r="AA3">
-        <v>10163085000</v>
-      </c>
-      <c r="AB3">
-        <v>54624000000</v>
+      <c r="AA3" t="str">
+        <v>2026-08-28T00:00:00Z</v>
       </c>
       <c r="AC3" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.iIBLUfZmUQ4kMoVj.Ckpn-Uob9HLP7YrWRTkTDbbfOIBHONTwrz8y1E4FjK0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="str">
+      <c r="B4" t="str">
         <v>66390314</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
+        <v>2026-10-15T00:00:00Z</v>
+      </c>
+      <c r="F4">
+        <v>10156213000</v>
+      </c>
+      <c r="G4" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I4" t="str">
+        <v>Jalan Biduri Raya, RT 10/RW 02 Kelurahan Batulicin, Kecamatan Batulicin, Kabupaten Tanah Bumbu, Provinsi Kalimantan Selatan</v>
+      </c>
+      <c r="J4" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="D4" t="str">
+      <c r="L4">
+        <v>55198624392</v>
+      </c>
+      <c r="M4">
+        <v>194</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="O4" t="str">
         <v>Tanah Bumbu (Kab.)</v>
       </c>
-      <c r="E4" t="str">
+      <c r="P4" t="str">
+        <v>K34</v>
+      </c>
+      <c r="T4">
+        <v>10163745000</v>
+      </c>
+      <c r="U4" t="str">
+        <v>Kalimantan Selatan</v>
+      </c>
+      <c r="W4">
+        <v>55483600000</v>
+      </c>
+      <c r="X4" t="str">
         <v>626131</v>
-      </c>
-      <c r="H4" t="str">
-        <v>Jalan Biduri Raya, RT 10/RW 02 Kelurahan Batulicin, Kecamatan Batulicin, Kabupaten Tanah Bumbu, Provinsi Kalimantan Selatan</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Kalimantan Selatan</v>
-      </c>
-      <c r="K4" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="L4">
-        <v>10156213000</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>2026-09-08T00:00:00Z</v>
-      </c>
-      <c r="S4" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="T4" t="str">
-        <v>2026-10-15T00:00:00Z</v>
-      </c>
-      <c r="V4" t="str">
-        <v>K34</v>
-      </c>
-      <c r="X4">
-        <v>55198624392</v>
-      </c>
-      <c r="Y4">
-        <v>194</v>
       </c>
       <c r="Z4">
         <v>2026</v>
       </c>
-      <c r="AA4">
-        <v>10163745000</v>
-      </c>
-      <c r="AB4">
-        <v>55483600000</v>
+      <c r="AA4" t="str">
+        <v>2026-09-08T00:00:00Z</v>
       </c>
       <c r="AC4" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.iIBLUfZmUQ4kMoVj.Ckpn-Uob9HLP7YrWRTkTDbbfOIBHONTwrz8y1E4FjK0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="str">
+      <c r="A5">
+        <v>712065</v>
+      </c>
+      <c r="B5" t="str">
         <v>67429813</v>
       </c>
-      <c r="B5" t="str">
+      <c r="C5" t="str">
+        <v>01.308.279.7-001.000</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-08-27T00:00:00Z</v>
+      </c>
+      <c r="E5" t="str">
+        <v>PT INERSIA AMPAK ENGINEERS</v>
+      </c>
+      <c r="F5">
+        <v>10144772000</v>
+      </c>
+      <c r="G5" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="H5">
+        <v>11760143000</v>
+      </c>
+      <c r="I5" t="str">
+        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
+      </c>
+      <c r="J5" t="str">
+        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
+      </c>
+      <c r="K5" t="str">
         <v>0013082797001000</v>
       </c>
-      <c r="C5" t="str">
-        <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
-      </c>
-      <c r="D5" t="str">
+      <c r="L5">
+        <v>2299921875</v>
+      </c>
+      <c r="M5">
+        <v>194</v>
+      </c>
+      <c r="N5" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="O5" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="E5" t="str">
+      <c r="P5" t="str">
+        <v>K34</v>
+      </c>
+      <c r="Q5">
+        <v>2089050250</v>
+      </c>
+      <c r="S5">
+        <v>2089050250</v>
+      </c>
+      <c r="T5">
+        <v>10151353000</v>
+      </c>
+      <c r="U5" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="V5">
+        <v>2089050250</v>
+      </c>
+      <c r="W5">
+        <v>2300000000</v>
+      </c>
+      <c r="X5" t="str">
         <v>626132</v>
       </c>
-      <c r="F5">
+      <c r="Y5">
         <v>2089050250</v>
-      </c>
-      <c r="G5" t="str">
-        <v>01.308.279.7-001.000</v>
-      </c>
-      <c r="H5" t="str">
-        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
-      </c>
-      <c r="J5" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="K5" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="L5">
-        <v>10144772000</v>
-      </c>
-      <c r="M5">
-        <v>2089050250</v>
-      </c>
-      <c r="O5">
-        <v>2089050250</v>
-      </c>
-      <c r="P5">
-        <v>2089050250</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>2026-07-22T00:00:00Z</v>
-      </c>
-      <c r="R5">
-        <v>712065</v>
-      </c>
-      <c r="S5" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="T5" t="str">
-        <v>2026-08-27T00:00:00Z</v>
-      </c>
-      <c r="U5">
-        <v>11760143000</v>
-      </c>
-      <c r="V5" t="str">
-        <v>K34</v>
-      </c>
-      <c r="W5" t="str">
-        <v>PT INERSIA AMPAK ENGINEERS</v>
-      </c>
-      <c r="X5">
-        <v>2299921875</v>
-      </c>
-      <c r="Y5">
-        <v>194</v>
       </c>
       <c r="Z5">
         <v>2026</v>
       </c>
-      <c r="AA5">
-        <v>10151353000</v>
-      </c>
-      <c r="AB5">
-        <v>2300000000</v>
+      <c r="AA5" t="str">
+        <v>2026-07-22T00:00:00Z</v>
       </c>
       <c r="AC5" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.iIBLUfZmUQ4kMoVj.Ckpn-Uob9HLP7YrWRTkTDbbfOIBHONTwrz8y1E4FjK0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="str">
-        <v>66390319</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      <c r="B6" t="str">
+        <v>67538410</v>
       </c>
       <c r="D6" t="str">
-        <v>Bulungan (Kab.)</v>
-      </c>
-      <c r="E6" t="str">
-        <v>626131</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
+        <v>2026-10-22T00:00:00Z</v>
+      </c>
+      <c r="F6">
+        <v>10158868000</v>
+      </c>
+      <c r="G6" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I6" t="str">
+        <v>Jl. Jend Gatot Subroto Kav 51</v>
       </c>
       <c r="J6" t="str">
-        <v>Kalimantan Utara</v>
-      </c>
-      <c r="K6" t="str">
-        <v>KEMENTERIAN</v>
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
       <c r="L6">
-        <v>10150225000</v>
-      </c>
-      <c r="Q6" t="str">
-        <v>2026-07-29T00:00:00Z</v>
-      </c>
-      <c r="S6" t="str">
+        <v>1904759785</v>
+      </c>
+      <c r="M6">
+        <v>194</v>
+      </c>
+      <c r="N6" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="T6" t="str">
-        <v>2026-09-17T00:00:00Z</v>
-      </c>
-      <c r="V6" t="str">
+      <c r="O6" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="P6" t="str">
         <v>K34</v>
       </c>
-      <c r="X6">
-        <v>94577629145</v>
-      </c>
-      <c r="Y6">
-        <v>194</v>
+      <c r="T6">
+        <v>10166654000</v>
+      </c>
+      <c r="U6" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="W6">
+        <v>2000000000</v>
+      </c>
+      <c r="X6" t="str">
+        <v>452677</v>
       </c>
       <c r="Z6">
         <v>2026</v>
       </c>
-      <c r="AA6">
-        <v>10157189000</v>
-      </c>
-      <c r="AB6">
-        <v>108024405000</v>
+      <c r="AA6" t="str">
+        <v>2026-09-08T00:00:00Z</v>
       </c>
       <c r="AC6" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.iIBLUfZmUQ4kMoVj.Ckpn-Uob9HLP7YrWRTkTDbbfOIBHONTwrz8y1E4FjK0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="str">
-        <v>67611590</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
+      <c r="B7" t="str">
+        <v>66390319</v>
       </c>
       <c r="D7" t="str">
-        <v>Jakarta Selatan (Kota)</v>
-      </c>
-      <c r="E7" t="str">
-        <v>452677</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Jl. Jend Gatot Subroto Kav 51</v>
+        <v>2026-09-17T00:00:00Z</v>
+      </c>
+      <c r="F7">
+        <v>10150225000</v>
+      </c>
+      <c r="G7" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I7" t="str">
+        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
       </c>
       <c r="J7" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="K7" t="str">
-        <v>KEMENTERIAN</v>
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
       <c r="L7">
-        <v>10152339000</v>
-      </c>
-      <c r="Q7" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="S7" t="str">
+        <v>94577629145</v>
+      </c>
+      <c r="M7">
+        <v>194</v>
+      </c>
+      <c r="N7" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="T7" t="str">
-        <v>2026-09-18T00:00:00Z</v>
-      </c>
-      <c r="V7" t="str">
+      <c r="O7" t="str">
+        <v>Bulungan (Kab.)</v>
+      </c>
+      <c r="P7" t="str">
         <v>K34</v>
       </c>
-      <c r="X7">
-        <v>294600000</v>
-      </c>
-      <c r="Y7">
-        <v>194</v>
+      <c r="T7">
+        <v>10157189000</v>
+      </c>
+      <c r="U7" t="str">
+        <v>Kalimantan Utara</v>
+      </c>
+      <c r="W7">
+        <v>108024405000</v>
+      </c>
+      <c r="X7" t="str">
+        <v>626131</v>
       </c>
       <c r="Z7">
         <v>2026</v>
       </c>
-      <c r="AA7">
-        <v>10159515000</v>
-      </c>
-      <c r="AB7">
-        <v>400000000</v>
+      <c r="AA7" t="str">
+        <v>2026-07-29T00:00:00Z</v>
       </c>
       <c r="AC7" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.iIBLUfZmUQ4kMoVj.Ckpn-Uob9HLP7YrWRTkTDbbfOIBHONTwrz8y1E4FjK0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="str">
-        <v>67592003</v>
-      </c>
-      <c r="C8" t="str">
+      <c r="B8" t="str">
+        <v>67611590</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-09-18T00:00:00Z</v>
+      </c>
+      <c r="F8">
+        <v>10152339000</v>
+      </c>
+      <c r="G8" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I8" t="str">
+        <v>Jl. Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="J8" t="str">
         <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
-      <c r="D8" t="str">
+      <c r="L8">
+        <v>294600000</v>
+      </c>
+      <c r="M8">
+        <v>194</v>
+      </c>
+      <c r="N8" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="O8" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="E8" t="str">
+      <c r="P8" t="str">
+        <v>K34</v>
+      </c>
+      <c r="T8">
+        <v>10159515000</v>
+      </c>
+      <c r="U8" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="W8">
+        <v>400000000</v>
+      </c>
+      <c r="X8" t="str">
         <v>452677</v>
-      </c>
-      <c r="H8" t="str">
-        <v>Jl Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="J8" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="K8" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="L8">
-        <v>10153666000</v>
-      </c>
-      <c r="Q8" t="str">
-        <v>2026-08-21T00:00:00Z</v>
-      </c>
-      <c r="S8" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="T8" t="str">
-        <v>2026-10-07T00:00:00Z</v>
-      </c>
-      <c r="V8" t="str">
-        <v>K34</v>
-      </c>
-      <c r="X8">
-        <v>12677050659</v>
-      </c>
-      <c r="Y8">
-        <v>194</v>
       </c>
       <c r="Z8">
         <v>2026</v>
       </c>
-      <c r="AA8">
-        <v>10160960000</v>
-      </c>
-      <c r="AB8">
-        <v>14699105000</v>
+      <c r="AA8" t="str">
+        <v>2026-08-05T00:00:00Z</v>
       </c>
       <c r="AC8" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.iIBLUfZmUQ4kMoVj.Ckpn-Uob9HLP7YrWRTkTDbbfOIBHONTwrz8y1E4FjK0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="str">
-        <v>67538462</v>
-      </c>
-      <c r="C9" t="str">
+      <c r="B9" t="str">
+        <v>67592003</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-10-07T00:00:00Z</v>
+      </c>
+      <c r="F9">
+        <v>10153666000</v>
+      </c>
+      <c r="G9" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I9" t="str">
+        <v>Jl Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="J9" t="str">
         <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
-      <c r="D9" t="str">
+      <c r="L9">
+        <v>12677050659</v>
+      </c>
+      <c r="M9">
+        <v>194</v>
+      </c>
+      <c r="N9" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="O9" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="E9" t="str">
+      <c r="P9" t="str">
+        <v>K34</v>
+      </c>
+      <c r="T9">
+        <v>10160960000</v>
+      </c>
+      <c r="U9" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="W9">
+        <v>14699105000</v>
+      </c>
+      <c r="X9" t="str">
         <v>452677</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Jl Jend Gatot Subroto Kav 51</v>
-      </c>
-      <c r="J9" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="K9" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="L9">
-        <v>10155417000</v>
-      </c>
-      <c r="Q9" t="str">
-        <v>2026-08-20T00:00:00Z</v>
-      </c>
-      <c r="S9" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="T9" t="str">
-        <v>2026-09-23T00:00:00Z</v>
-      </c>
-      <c r="V9" t="str">
-        <v>K34</v>
-      </c>
-      <c r="X9">
-        <v>646650000</v>
-      </c>
-      <c r="Y9">
-        <v>194</v>
       </c>
       <c r="Z9">
         <v>2026</v>
       </c>
-      <c r="AA9">
-        <v>10162858000</v>
-      </c>
-      <c r="AB9">
-        <v>654750000</v>
+      <c r="AA9" t="str">
+        <v>2026-08-21T00:00:00Z</v>
       </c>
       <c r="AC9" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.iIBLUfZmUQ4kMoVj.Ckpn-Uob9HLP7YrWRTkTDbbfOIBHONTwrz8y1E4FjK0</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="str">
-        <v>66390318</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      <c r="B10" t="str">
+        <v>67538462</v>
       </c>
       <c r="D10" t="str">
-        <v>Halmahera Selatan (Kab.)</v>
-      </c>
-      <c r="E10" t="str">
-        <v>626131</v>
-      </c>
-      <c r="H10" t="str">
-        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
+        <v>2026-09-23T00:00:00Z</v>
+      </c>
+      <c r="F10">
+        <v>10155417000</v>
+      </c>
+      <c r="G10" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I10" t="str">
+        <v>Jl Jend Gatot Subroto Kav 51</v>
       </c>
       <c r="J10" t="str">
-        <v>Maluku Utara</v>
-      </c>
-      <c r="K10" t="str">
-        <v>KEMENTERIAN</v>
+        <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
       <c r="L10">
-        <v>10151157000</v>
-      </c>
-      <c r="Q10" t="str">
-        <v>2026-08-05T00:00:00Z</v>
-      </c>
-      <c r="S10" t="str">
+        <v>646650000</v>
+      </c>
+      <c r="M10">
+        <v>194</v>
+      </c>
+      <c r="N10" t="str">
         <v>Kementerian Ketenagakerjaan</v>
       </c>
-      <c r="T10" t="str">
-        <v>2026-09-16T00:00:00Z</v>
-      </c>
-      <c r="V10" t="str">
+      <c r="O10" t="str">
+        <v>Jakarta Selatan (Kota)</v>
+      </c>
+      <c r="P10" t="str">
         <v>K34</v>
       </c>
-      <c r="X10">
-        <v>72210016000</v>
-      </c>
-      <c r="Y10">
-        <v>194</v>
+      <c r="T10">
+        <v>10162858000</v>
+      </c>
+      <c r="U10" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="W10">
+        <v>654750000</v>
+      </c>
+      <c r="X10" t="str">
+        <v>452677</v>
       </c>
       <c r="Z10">
         <v>2026</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" t="str">
+        <v>2026-08-20T00:00:00Z</v>
+      </c>
+      <c r="AC10" t="str">
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="str">
+        <v>66390318</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-09-16T00:00:00Z</v>
+      </c>
+      <c r="F11">
+        <v>10151157000</v>
+      </c>
+      <c r="G11" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="I11" t="str">
+        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
+      </c>
+      <c r="L11">
+        <v>72210016000</v>
+      </c>
+      <c r="M11">
+        <v>194</v>
+      </c>
+      <c r="N11" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="O11" t="str">
+        <v>Halmahera Selatan (Kab.)</v>
+      </c>
+      <c r="P11" t="str">
+        <v>K34</v>
+      </c>
+      <c r="T11">
         <v>10158222000</v>
       </c>
-      <c r="AB10">
+      <c r="U11" t="str">
+        <v>Maluku Utara</v>
+      </c>
+      <c r="W11">
         <v>72311690000</v>
       </c>
-      <c r="AC10" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.iIBLUfZmUQ4kMoVj.Ckpn-Uob9HLP7YrWRTkTDbbfOIBHONTwrz8y1E4FjK0</v>
+      <c r="X11" t="str">
+        <v>626131</v>
+      </c>
+      <c r="Z11">
+        <v>2026</v>
+      </c>
+      <c r="AA11" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="AC11" t="str">
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AC10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AC11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
+++ b/data/data_update/tender_selesai_nilai/tender-selesai-nilai_2026.xlsx
@@ -401,678 +401,678 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>kd_penyedia</v>
+        <v>lokasi_pekerjaan</v>
       </c>
       <c r="B1" t="str">
-        <v>kd_rup_paket</v>
+        <v>nilai_penawaran</v>
       </c>
       <c r="C1" t="str">
-        <v>npwp_penyedia</v>
+        <v>nilai_kontrak</v>
       </c>
       <c r="D1" t="str">
-        <v>tgl_penetapan_pemenang</v>
+        <v>tahun_anggaran</v>
       </c>
       <c r="E1" t="str">
-        <v>nama_penyedia</v>
+        <v>kd_klpd</v>
       </c>
       <c r="F1" t="str">
         <v>kd_paket</v>
       </c>
       <c r="G1" t="str">
-        <v>jenis_klpd</v>
+        <v>nama_penyedia</v>
       </c>
       <c r="H1" t="str">
-        <v>psr_id</v>
+        <v>nama_klpd</v>
       </c>
       <c r="I1" t="str">
-        <v>lokasi_pekerjaan</v>
+        <v>nilai_terkoreksi</v>
       </c>
       <c r="J1" t="str">
         <v>nama_satker</v>
       </c>
       <c r="K1" t="str">
-        <v>npwp_16_penyedia</v>
+        <v>kd_lpse</v>
       </c>
       <c r="L1" t="str">
-        <v>hps</v>
+        <v>psr_id</v>
       </c>
       <c r="M1" t="str">
-        <v>kd_lpse</v>
+        <v>jenis_klpd</v>
       </c>
       <c r="N1" t="str">
-        <v>nama_klpd</v>
+        <v>tgl_pengumuman_tender</v>
       </c>
       <c r="O1" t="str">
-        <v>kabkota</v>
+        <v>kd_tender</v>
       </c>
       <c r="P1" t="str">
-        <v>kd_klpd</v>
+        <v>kd_penyedia</v>
       </c>
       <c r="Q1" t="str">
-        <v>nilai_kontrak</v>
+        <v>kd_satker</v>
       </c>
       <c r="R1" t="str">
         <v>nilai_pdn_kontrak</v>
       </c>
       <c r="S1" t="str">
-        <v>nilai_penawaran</v>
+        <v>npwp_16_penyedia</v>
       </c>
       <c r="T1" t="str">
-        <v>kd_tender</v>
+        <v>npwp_penyedia</v>
       </c>
       <c r="U1" t="str">
+        <v>pagu</v>
+      </c>
+      <c r="V1" t="str">
+        <v>hps</v>
+      </c>
+      <c r="W1" t="str">
+        <v>nilai_umk_kontrak</v>
+      </c>
+      <c r="X1" t="str">
         <v>provinsi</v>
       </c>
-      <c r="V1" t="str">
-        <v>nilai_terkoreksi</v>
-      </c>
-      <c r="W1" t="str">
-        <v>pagu</v>
-      </c>
-      <c r="X1" t="str">
-        <v>kd_satker</v>
-      </c>
       <c r="Y1" t="str">
+        <v>kabkota</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>kd_rup_paket</v>
+      </c>
+      <c r="AA1" t="str">
         <v>nilai_negosiasi</v>
       </c>
-      <c r="Z1" t="str">
-        <v>tahun_anggaran</v>
-      </c>
-      <c r="AA1" t="str">
-        <v>tgl_pengumuman_tender</v>
-      </c>
       <c r="AB1" t="str">
-        <v>nilai_umk_kontrak</v>
+        <v>tgl_penetapan_pemenang</v>
       </c>
       <c r="AC1" t="str">
         <v>last_update_ref</v>
       </c>
     </row>
     <row r="2">
-      <c r="B2" t="str">
-        <v>66390312</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2026-10-01T00:00:00Z</v>
+      <c r="A2" t="str">
+        <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
+      </c>
+      <c r="D2">
+        <v>2026</v>
+      </c>
+      <c r="E2" t="str">
+        <v>K34</v>
       </c>
       <c r="F2">
         <v>10152741000</v>
       </c>
-      <c r="G2" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Jalan Merapi Raya No. 89, Kelurahan Panorama, Kecamatan Singaran Pati, Kota Bengkulu, Provinsi Bengkulu</v>
+      <c r="H2" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="J2" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="L2">
+      <c r="K2">
+        <v>194</v>
+      </c>
+      <c r="M2" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="N2" t="str">
+        <v>2026-08-21T00:00:00Z</v>
+      </c>
+      <c r="O2">
+        <v>10159959000</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>626131</v>
+      </c>
+      <c r="U2">
+        <v>63441052000</v>
+      </c>
+      <c r="V2">
         <v>51439625000</v>
       </c>
-      <c r="M2">
-        <v>194</v>
-      </c>
-      <c r="N2" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="O2" t="str">
+      <c r="X2" t="str">
+        <v>Bengkulu</v>
+      </c>
+      <c r="Y2" t="str">
         <v>Bengkulu (Kota)</v>
       </c>
-      <c r="P2" t="str">
-        <v>K34</v>
-      </c>
-      <c r="T2">
-        <v>10159959000</v>
-      </c>
-      <c r="U2" t="str">
-        <v>Bengkulu</v>
-      </c>
-      <c r="W2">
-        <v>63441052000</v>
-      </c>
-      <c r="X2" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Z2">
-        <v>2026</v>
-      </c>
-      <c r="AA2" t="str">
-        <v>2026-08-21T00:00:00Z</v>
+      <c r="Z2" t="str">
+        <v>66390312</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>2026-10-01T00:00:00Z</v>
       </c>
       <c r="AC2" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.7lJvHHveywTU6tOK.FxLdoeEfr9ANwJI0MauFE7YzlQZkE0YoAM7-Ri13HoQ</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" t="str">
-        <v>66390327</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-10-06T00:00:00Z</v>
+      <c r="A3" t="str">
+        <v>Desa Batu Besar, Kecamatan Nongsa, Kota Batam, Provinsi Kepulauan Riau</v>
+      </c>
+      <c r="D3">
+        <v>2026</v>
+      </c>
+      <c r="E3" t="str">
+        <v>K34</v>
       </c>
       <c r="F3">
         <v>10155602000</v>
       </c>
-      <c r="G3" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Desa Batu Besar, Kecamatan Nongsa, Kota Batam, Provinsi Kepulauan Riau</v>
+      <c r="H3" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="J3" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="L3">
+      <c r="K3">
+        <v>194</v>
+      </c>
+      <c r="M3" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="N3" t="str">
+        <v>2026-08-28T00:00:00Z</v>
+      </c>
+      <c r="O3">
+        <v>10163085000</v>
+      </c>
+      <c r="Q3" t="str">
+        <v>626131</v>
+      </c>
+      <c r="U3">
+        <v>54624000000</v>
+      </c>
+      <c r="V3">
         <v>54472055602.06</v>
       </c>
-      <c r="M3">
-        <v>194</v>
-      </c>
-      <c r="N3" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="O3" t="str">
+      <c r="X3" t="str">
+        <v>Kepulauan Riau</v>
+      </c>
+      <c r="Y3" t="str">
         <v>Batam (Kota)</v>
       </c>
-      <c r="P3" t="str">
-        <v>K34</v>
-      </c>
-      <c r="T3">
-        <v>10163085000</v>
-      </c>
-      <c r="U3" t="str">
-        <v>Kepulauan Riau</v>
-      </c>
-      <c r="W3">
-        <v>54624000000</v>
-      </c>
-      <c r="X3" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Z3">
-        <v>2026</v>
-      </c>
-      <c r="AA3" t="str">
-        <v>2026-08-28T00:00:00Z</v>
+      <c r="Z3" t="str">
+        <v>66390327</v>
+      </c>
+      <c r="AB3" t="str">
+        <v>2026-10-06T00:00:00Z</v>
       </c>
       <c r="AC3" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.7lJvHHveywTU6tOK.FxLdoeEfr9ANwJI0MauFE7YzlQZkE0YoAM7-Ri13HoQ</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" t="str">
-        <v>66390314</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-10-15T00:00:00Z</v>
+      <c r="A4" t="str">
+        <v>Jalan Biduri Raya, RT 10/RW 02 Kelurahan Batulicin, Kecamatan Batulicin, Kabupaten Tanah Bumbu, Provinsi Kalimantan Selatan</v>
+      </c>
+      <c r="D4">
+        <v>2026</v>
+      </c>
+      <c r="E4" t="str">
+        <v>K34</v>
       </c>
       <c r="F4">
         <v>10156213000</v>
       </c>
-      <c r="G4" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="I4" t="str">
-        <v>Jalan Biduri Raya, RT 10/RW 02 Kelurahan Batulicin, Kecamatan Batulicin, Kabupaten Tanah Bumbu, Provinsi Kalimantan Selatan</v>
+      <c r="H4" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="J4" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="L4">
+      <c r="K4">
+        <v>194</v>
+      </c>
+      <c r="M4" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="N4" t="str">
+        <v>2026-09-08T00:00:00Z</v>
+      </c>
+      <c r="O4">
+        <v>10163745000</v>
+      </c>
+      <c r="Q4" t="str">
+        <v>626131</v>
+      </c>
+      <c r="U4">
+        <v>55483600000</v>
+      </c>
+      <c r="V4">
         <v>55198624392</v>
       </c>
-      <c r="M4">
-        <v>194</v>
-      </c>
-      <c r="N4" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="O4" t="str">
+      <c r="X4" t="str">
+        <v>Kalimantan Selatan</v>
+      </c>
+      <c r="Y4" t="str">
         <v>Tanah Bumbu (Kab.)</v>
       </c>
-      <c r="P4" t="str">
-        <v>K34</v>
-      </c>
-      <c r="T4">
-        <v>10163745000</v>
-      </c>
-      <c r="U4" t="str">
-        <v>Kalimantan Selatan</v>
-      </c>
-      <c r="W4">
-        <v>55483600000</v>
-      </c>
-      <c r="X4" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Z4">
-        <v>2026</v>
-      </c>
-      <c r="AA4" t="str">
-        <v>2026-09-08T00:00:00Z</v>
+      <c r="Z4" t="str">
+        <v>66390314</v>
+      </c>
+      <c r="AB4" t="str">
+        <v>2026-10-15T00:00:00Z</v>
       </c>
       <c r="AC4" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.7lJvHHveywTU6tOK.FxLdoeEfr9ANwJI0MauFE7YzlQZkE0YoAM7-Ri13HoQ</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>712065</v>
-      </c>
-      <c r="B5" t="str">
-        <v>67429813</v>
-      </c>
-      <c r="C5" t="str">
-        <v>01.308.279.7-001.000</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-08-27T00:00:00Z</v>
+      <c r="A5" t="str">
+        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
+      </c>
+      <c r="B5">
+        <v>2089050250</v>
+      </c>
+      <c r="C5">
+        <v>2089050250</v>
+      </c>
+      <c r="D5">
+        <v>2026</v>
       </c>
       <c r="E5" t="str">
-        <v>PT INERSIA AMPAK ENGINEERS</v>
+        <v>K34</v>
       </c>
       <c r="F5">
         <v>10144772000</v>
       </c>
       <c r="G5" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="H5">
-        <v>11760143000</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Gedung Vokasi Jalan Jenderal Gatot Subroto Kaveling 44 Jakarta Selatan DKI Jakarta</v>
+        <v>PT INERSIA AMPAK ENGINEERS</v>
+      </c>
+      <c r="H5" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
+      </c>
+      <c r="I5">
+        <v>2089050250</v>
       </c>
       <c r="J5" t="str">
         <v>Direktorat Bina Penyelenggaraan Pelatihan Vokasi dan Pemagangan</v>
       </c>
-      <c r="K5" t="str">
+      <c r="K5">
+        <v>194</v>
+      </c>
+      <c r="L5">
+        <v>11760143000</v>
+      </c>
+      <c r="M5" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="N5" t="str">
+        <v>2026-07-22T00:00:00Z</v>
+      </c>
+      <c r="O5">
+        <v>10151353000</v>
+      </c>
+      <c r="P5">
+        <v>712065</v>
+      </c>
+      <c r="Q5" t="str">
+        <v>626132</v>
+      </c>
+      <c r="S5" t="str">
         <v>0013082797001000</v>
       </c>
-      <c r="L5">
+      <c r="T5" t="str">
+        <v>01.308.279.7-001.000</v>
+      </c>
+      <c r="U5">
+        <v>2300000000</v>
+      </c>
+      <c r="V5">
         <v>2299921875</v>
       </c>
-      <c r="M5">
-        <v>194</v>
-      </c>
-      <c r="N5" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="O5" t="str">
+      <c r="X5" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y5" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="P5" t="str">
-        <v>K34</v>
-      </c>
-      <c r="Q5">
+      <c r="Z5" t="str">
+        <v>67429813</v>
+      </c>
+      <c r="AA5">
         <v>2089050250</v>
       </c>
-      <c r="S5">
-        <v>2089050250</v>
-      </c>
-      <c r="T5">
-        <v>10151353000</v>
-      </c>
-      <c r="U5" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="V5">
-        <v>2089050250</v>
-      </c>
-      <c r="W5">
-        <v>2300000000</v>
-      </c>
-      <c r="X5" t="str">
-        <v>626132</v>
-      </c>
-      <c r="Y5">
-        <v>2089050250</v>
-      </c>
-      <c r="Z5">
-        <v>2026</v>
-      </c>
-      <c r="AA5" t="str">
-        <v>2026-07-22T00:00:00Z</v>
+      <c r="AB5" t="str">
+        <v>2026-08-27T00:00:00Z</v>
       </c>
       <c r="AC5" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.7lJvHHveywTU6tOK.FxLdoeEfr9ANwJI0MauFE7YzlQZkE0YoAM7-Ri13HoQ</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="str">
-        <v>67538410</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-10-22T00:00:00Z</v>
+      <c r="A6" t="str">
+        <v>Jl. Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="D6">
+        <v>2026</v>
+      </c>
+      <c r="E6" t="str">
+        <v>K34</v>
       </c>
       <c r="F6">
         <v>10158868000</v>
       </c>
-      <c r="G6" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="I6" t="str">
-        <v>Jl. Jend Gatot Subroto Kav 51</v>
+      <c r="H6" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="J6" t="str">
         <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
-      <c r="L6">
+      <c r="K6">
+        <v>194</v>
+      </c>
+      <c r="M6" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="N6" t="str">
+        <v>2026-09-08T00:00:00Z</v>
+      </c>
+      <c r="O6">
+        <v>10166654000</v>
+      </c>
+      <c r="Q6" t="str">
+        <v>452677</v>
+      </c>
+      <c r="U6">
+        <v>2000000000</v>
+      </c>
+      <c r="V6">
         <v>1904759785</v>
       </c>
-      <c r="M6">
-        <v>194</v>
-      </c>
-      <c r="N6" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="O6" t="str">
+      <c r="X6" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y6" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="P6" t="str">
-        <v>K34</v>
-      </c>
-      <c r="T6">
-        <v>10166654000</v>
-      </c>
-      <c r="U6" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="W6">
-        <v>2000000000</v>
-      </c>
-      <c r="X6" t="str">
-        <v>452677</v>
-      </c>
-      <c r="Z6">
-        <v>2026</v>
-      </c>
-      <c r="AA6" t="str">
-        <v>2026-09-08T00:00:00Z</v>
+      <c r="Z6" t="str">
+        <v>67538410</v>
+      </c>
+      <c r="AB6" t="str">
+        <v>2026-10-22T00:00:00Z</v>
       </c>
       <c r="AC6" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.7lJvHHveywTU6tOK.FxLdoeEfr9ANwJI0MauFE7YzlQZkE0YoAM7-Ri13HoQ</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="str">
-        <v>66390319</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-09-17T00:00:00Z</v>
+      <c r="A7" t="str">
+        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
+      </c>
+      <c r="D7">
+        <v>2026</v>
+      </c>
+      <c r="E7" t="str">
+        <v>K34</v>
       </c>
       <c r="F7">
         <v>10150225000</v>
       </c>
-      <c r="G7" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Jalan Nasional Poros Bulungan - Malinau, Desa Seriang, Kecamatan Tanjung Selor, Kabupaten Bulungan, Provinsi Kalimantan Utara</v>
+      <c r="H7" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="J7" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="L7">
+      <c r="K7">
+        <v>194</v>
+      </c>
+      <c r="M7" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="N7" t="str">
+        <v>2026-07-29T00:00:00Z</v>
+      </c>
+      <c r="O7">
+        <v>10157189000</v>
+      </c>
+      <c r="Q7" t="str">
+        <v>626131</v>
+      </c>
+      <c r="U7">
+        <v>108024405000</v>
+      </c>
+      <c r="V7">
         <v>94577629145</v>
       </c>
-      <c r="M7">
-        <v>194</v>
-      </c>
-      <c r="N7" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="O7" t="str">
+      <c r="X7" t="str">
+        <v>Kalimantan Utara</v>
+      </c>
+      <c r="Y7" t="str">
         <v>Bulungan (Kab.)</v>
       </c>
-      <c r="P7" t="str">
-        <v>K34</v>
-      </c>
-      <c r="T7">
-        <v>10157189000</v>
-      </c>
-      <c r="U7" t="str">
-        <v>Kalimantan Utara</v>
-      </c>
-      <c r="W7">
-        <v>108024405000</v>
-      </c>
-      <c r="X7" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Z7">
-        <v>2026</v>
-      </c>
-      <c r="AA7" t="str">
-        <v>2026-07-29T00:00:00Z</v>
+      <c r="Z7" t="str">
+        <v>66390319</v>
+      </c>
+      <c r="AB7" t="str">
+        <v>2026-09-17T00:00:00Z</v>
       </c>
       <c r="AC7" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.7lJvHHveywTU6tOK.FxLdoeEfr9ANwJI0MauFE7YzlQZkE0YoAM7-Ri13HoQ</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="str">
-        <v>67611590</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-09-18T00:00:00Z</v>
+      <c r="A8" t="str">
+        <v>Jl. Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="D8">
+        <v>2026</v>
+      </c>
+      <c r="E8" t="str">
+        <v>K34</v>
       </c>
       <c r="F8">
         <v>10152339000</v>
       </c>
-      <c r="G8" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Jl. Jend Gatot Subroto Kav 51</v>
+      <c r="H8" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="J8" t="str">
         <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
-      <c r="L8">
+      <c r="K8">
+        <v>194</v>
+      </c>
+      <c r="M8" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="N8" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="O8">
+        <v>10159515000</v>
+      </c>
+      <c r="Q8" t="str">
+        <v>452677</v>
+      </c>
+      <c r="U8">
+        <v>400000000</v>
+      </c>
+      <c r="V8">
         <v>294600000</v>
       </c>
-      <c r="M8">
-        <v>194</v>
-      </c>
-      <c r="N8" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="O8" t="str">
+      <c r="X8" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y8" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="P8" t="str">
-        <v>K34</v>
-      </c>
-      <c r="T8">
-        <v>10159515000</v>
-      </c>
-      <c r="U8" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="W8">
-        <v>400000000</v>
-      </c>
-      <c r="X8" t="str">
-        <v>452677</v>
-      </c>
-      <c r="Z8">
-        <v>2026</v>
-      </c>
-      <c r="AA8" t="str">
-        <v>2026-08-05T00:00:00Z</v>
+      <c r="Z8" t="str">
+        <v>67611590</v>
+      </c>
+      <c r="AB8" t="str">
+        <v>2026-09-18T00:00:00Z</v>
       </c>
       <c r="AC8" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.7lJvHHveywTU6tOK.FxLdoeEfr9ANwJI0MauFE7YzlQZkE0YoAM7-Ri13HoQ</v>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="str">
-        <v>67592003</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-10-07T00:00:00Z</v>
+      <c r="A9" t="str">
+        <v>Jl Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="D9">
+        <v>2026</v>
+      </c>
+      <c r="E9" t="str">
+        <v>K34</v>
       </c>
       <c r="F9">
         <v>10153666000</v>
       </c>
-      <c r="G9" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="I9" t="str">
-        <v>Jl Jend Gatot Subroto Kav 51</v>
+      <c r="H9" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="J9" t="str">
         <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
-      <c r="L9">
+      <c r="K9">
+        <v>194</v>
+      </c>
+      <c r="M9" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="N9" t="str">
+        <v>2026-08-21T00:00:00Z</v>
+      </c>
+      <c r="O9">
+        <v>10160960000</v>
+      </c>
+      <c r="Q9" t="str">
+        <v>452677</v>
+      </c>
+      <c r="U9">
+        <v>14699105000</v>
+      </c>
+      <c r="V9">
         <v>12677050659</v>
       </c>
-      <c r="M9">
-        <v>194</v>
-      </c>
-      <c r="N9" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="O9" t="str">
+      <c r="X9" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y9" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="P9" t="str">
-        <v>K34</v>
-      </c>
-      <c r="T9">
-        <v>10160960000</v>
-      </c>
-      <c r="U9" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="W9">
-        <v>14699105000</v>
-      </c>
-      <c r="X9" t="str">
-        <v>452677</v>
-      </c>
-      <c r="Z9">
-        <v>2026</v>
-      </c>
-      <c r="AA9" t="str">
-        <v>2026-08-21T00:00:00Z</v>
+      <c r="Z9" t="str">
+        <v>67592003</v>
+      </c>
+      <c r="AB9" t="str">
+        <v>2026-10-07T00:00:00Z</v>
       </c>
       <c r="AC9" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.7lJvHHveywTU6tOK.FxLdoeEfr9ANwJI0MauFE7YzlQZkE0YoAM7-Ri13HoQ</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="str">
-        <v>67538462</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-09-23T00:00:00Z</v>
+      <c r="A10" t="str">
+        <v>Jl Jend Gatot Subroto Kav 51</v>
+      </c>
+      <c r="D10">
+        <v>2026</v>
+      </c>
+      <c r="E10" t="str">
+        <v>K34</v>
       </c>
       <c r="F10">
         <v>10155417000</v>
       </c>
-      <c r="G10" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="I10" t="str">
-        <v>Jl Jend Gatot Subroto Kav 51</v>
+      <c r="H10" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="J10" t="str">
         <v>Badan Perencanaan dan Pengembangan Ketenagakerjaan</v>
       </c>
-      <c r="L10">
+      <c r="K10">
+        <v>194</v>
+      </c>
+      <c r="M10" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="N10" t="str">
+        <v>2026-08-20T00:00:00Z</v>
+      </c>
+      <c r="O10">
+        <v>10162858000</v>
+      </c>
+      <c r="Q10" t="str">
+        <v>452677</v>
+      </c>
+      <c r="U10">
+        <v>654750000</v>
+      </c>
+      <c r="V10">
         <v>646650000</v>
       </c>
-      <c r="M10">
-        <v>194</v>
-      </c>
-      <c r="N10" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="O10" t="str">
+      <c r="X10" t="str">
+        <v>DKI Jakarta</v>
+      </c>
+      <c r="Y10" t="str">
         <v>Jakarta Selatan (Kota)</v>
       </c>
-      <c r="P10" t="str">
-        <v>K34</v>
-      </c>
-      <c r="T10">
-        <v>10162858000</v>
-      </c>
-      <c r="U10" t="str">
-        <v>DKI Jakarta</v>
-      </c>
-      <c r="W10">
-        <v>654750000</v>
-      </c>
-      <c r="X10" t="str">
-        <v>452677</v>
-      </c>
-      <c r="Z10">
-        <v>2026</v>
-      </c>
-      <c r="AA10" t="str">
-        <v>2026-08-20T00:00:00Z</v>
+      <c r="Z10" t="str">
+        <v>67538462</v>
+      </c>
+      <c r="AB10" t="str">
+        <v>2026-09-23T00:00:00Z</v>
       </c>
       <c r="AC10" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.7lJvHHveywTU6tOK.FxLdoeEfr9ANwJI0MauFE7YzlQZkE0YoAM7-Ri13HoQ</v>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="str">
-        <v>66390318</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-09-16T00:00:00Z</v>
+      <c r="A11" t="str">
+        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
+      </c>
+      <c r="D11">
+        <v>2026</v>
+      </c>
+      <c r="E11" t="str">
+        <v>K34</v>
       </c>
       <c r="F11">
         <v>10151157000</v>
       </c>
-      <c r="G11" t="str">
-        <v>KEMENTERIAN</v>
-      </c>
-      <c r="I11" t="str">
-        <v>Desa Panamboang, Kecamatan Bacan Selatan, Kabupaten Halmahera Selatan, Provinsi Maluku Utara</v>
+      <c r="H11" t="str">
+        <v>Kementerian Ketenagakerjaan</v>
       </c>
       <c r="J11" t="str">
         <v>Direktorat Bina Kelembagaan Pelatihan Vokasi</v>
       </c>
-      <c r="L11">
+      <c r="K11">
+        <v>194</v>
+      </c>
+      <c r="M11" t="str">
+        <v>KEMENTERIAN</v>
+      </c>
+      <c r="N11" t="str">
+        <v>2026-08-05T00:00:00Z</v>
+      </c>
+      <c r="O11">
+        <v>10158222000</v>
+      </c>
+      <c r="Q11" t="str">
+        <v>626131</v>
+      </c>
+      <c r="U11">
+        <v>72311690000</v>
+      </c>
+      <c r="V11">
         <v>72210016000</v>
       </c>
-      <c r="M11">
-        <v>194</v>
-      </c>
-      <c r="N11" t="str">
-        <v>Kementerian Ketenagakerjaan</v>
-      </c>
-      <c r="O11" t="str">
+      <c r="X11" t="str">
+        <v>Maluku Utara</v>
+      </c>
+      <c r="Y11" t="str">
         <v>Halmahera Selatan (Kab.)</v>
       </c>
-      <c r="P11" t="str">
-        <v>K34</v>
-      </c>
-      <c r="T11">
-        <v>10158222000</v>
-      </c>
-      <c r="U11" t="str">
-        <v>Maluku Utara</v>
-      </c>
-      <c r="W11">
-        <v>72311690000</v>
-      </c>
-      <c r="X11" t="str">
-        <v>626131</v>
-      </c>
-      <c r="Z11">
-        <v>2026</v>
-      </c>
-      <c r="AA11" t="str">
-        <v>2026-08-05T00:00:00Z</v>
+      <c r="Z11" t="str">
+        <v>66390318</v>
+      </c>
+      <c r="AB11" t="str">
+        <v>2026-09-16T00:00:00Z</v>
       </c>
       <c r="AC11" t="str">
-        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.cdT9sbzEC9GgDA12.Pwct9a-EC2RJ7ZpeuESUDSe5ll3pK8EbKDK_Ja-paFo</v>
+        <v>cc820c5f-e6ba-5337-bc51-523cc40dc3a2.7lJvHHveywTU6tOK.FxLdoeEfr9ANwJI0MauFE7YzlQZkE0YoAM7-Ri13HoQ</v>
       </c>
     </row>
   </sheetData>
